--- a/data/hachioji_kousei_houkan.xlsx
+++ b/data/hachioji_kousei_houkan.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0000000"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="167" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +51,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,11 +426,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>指定自立支援医療機関（育成・更生医療）指定一覧【訪問看護事業者等】（令和8年6月1日現在）</t>
         </is>
       </c>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
       <c r="Z1" t="inlineStr">
         <is>
           <t>有効期限到来により失効(～平成年月日）</t>
@@ -438,7 +451,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
@@ -496,7 +509,7 @@
           <t>都発番号</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>医療種別</t>
         </is>
@@ -511,12 +524,12 @@
           <t>更生医療</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>指定年月</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>廃止・
 辞退・
@@ -555,17 +568,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>コード</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>都13/訪問看6</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>重複</t>
         </is>
@@ -580,7 +593,7 @@
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>区市町村名</t>
         </is>
@@ -617,20 +630,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>7191778</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1367191778</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -640,12 +653,12 @@
           <t>城山訪問看護ステーション</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>193-0826</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -681,7 +694,7 @@
       <c r="P4" t="n">
         <v>40210</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="Q4" s="3" t="n">
         <v>40210</v>
       </c>
       <c r="R4" t="inlineStr">
@@ -697,7 +710,7 @@
           <t>3八福障収第1125号</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -711,22 +724,25 @@
       <c r="X4" t="n">
         <v>42202</v>
       </c>
+      <c r="Z4" s="1" t="n"/>
+      <c r="AA4" s="1" t="n"/>
+      <c r="AB4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>7399256</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1367399256</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -741,7 +757,7 @@
           <t>192-0082</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -777,7 +793,7 @@
       <c r="P5" t="n">
         <v>38808</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="Q5" s="3" t="n">
         <v>39114</v>
       </c>
       <c r="R5" t="inlineStr">
@@ -793,7 +809,7 @@
           <t>6八福障第5389号</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -839,20 +855,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>3-3</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>7192552</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1367192552</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -867,7 +883,7 @@
           <t>192-0066</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -903,7 +919,7 @@
       <c r="P6" t="n">
         <v>38808</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="Q6" s="3" t="n">
         <v>39114</v>
       </c>
       <c r="R6" t="inlineStr">
@@ -919,7 +935,7 @@
           <t>6八福障第6318号</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -950,7 +966,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-4</t>
         </is>
@@ -960,15 +976,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>7198534</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1367198534</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -978,12 +994,12 @@
           <t>たちばなスマイルケア訪問看護ステーション</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>193-0801</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1009,7 +1025,7 @@
       <c r="P7" t="n">
         <v>39417</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="Q7" s="3" t="n">
         <v>39417</v>
       </c>
       <c r="R7" t="inlineStr">
@@ -1017,7 +1033,8 @@
           <t>19福保障計第969号</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="S7" s="1" t="n"/>
+      <c r="U7" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1041,7 +1058,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>3-5</t>
         </is>
@@ -1051,15 +1068,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>7198997</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1367198997</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1074,12 +1091,12 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>八王子市南大沢１－１８－１１　シュガーハイツ南大沢Ａ１０３</t>
         </is>
@@ -1100,7 +1117,7 @@
       <c r="P8" t="n">
         <v>39783</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="Q8" s="3" t="n">
         <v>39783</v>
       </c>
       <c r="R8" t="inlineStr">
@@ -1108,7 +1125,7 @@
           <t>20福保障計第881号</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1132,20 +1149,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>3-6</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>7199839</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1367199839</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1155,12 +1172,12 @@
           <t>城山みなみ訪問看護ステーション</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>193-0844</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1196,7 +1213,7 @@
       <c r="P9" t="n">
         <v>40210</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="Q9" s="3" t="n">
         <v>40210</v>
       </c>
       <c r="R9" t="inlineStr">
@@ -1212,7 +1229,7 @@
           <t>3八福障収第1143号</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1226,9 +1243,12 @@
       <c r="X9" t="n">
         <v>42202</v>
       </c>
+      <c r="Z9" s="1" t="n"/>
+      <c r="AA9" s="1" t="n"/>
+      <c r="AB9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
@@ -1238,15 +1258,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="1" t="n">
         <v>7292923</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1367292923</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1292,10 +1312,10 @@
       <c r="P10" t="n">
         <v>41487</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="Q10" s="3" t="n">
         <v>41487</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>25福保障計第598号</t>
         </is>
@@ -1314,7 +1334,7 @@
       <c r="Y10" t="n">
         <v>42904</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" s="1" t="inlineStr">
         <is>
           <t>休止届（平成28年5月1日休止、人員不足）</t>
         </is>
@@ -1326,7 +1346,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>3-8</t>
         </is>
@@ -1336,15 +1356,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2" t="n">
         <v>7293095</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1367293095</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1354,12 +1374,12 @@
           <t>ミモザ在宅療養支援ステーション京王堀之内</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>192-0355</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1379,7 +1399,7 @@
           <t>ミモザ株式会社</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>140-0004</t>
         </is>
@@ -1395,7 +1415,7 @@
       <c r="P11" t="n">
         <v>41548</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="Q11" s="3" t="n">
         <v>41548</v>
       </c>
       <c r="R11" t="inlineStr">
@@ -1403,6 +1423,7 @@
           <t>25福保障計第894号</t>
         </is>
       </c>
+      <c r="T11" s="1" t="n"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
@@ -1432,7 +1453,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>3-9</t>
         </is>
@@ -1442,15 +1463,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>7293707</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1367293707</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1465,7 +1486,7 @@
           <t>192-0084</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1485,12 +1506,12 @@
           <t>柳屋食品株式会社</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>321-4308</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>栃木県真岡市中郷３３９－２</t>
         </is>
@@ -1501,7 +1522,7 @@
       <c r="P12" t="n">
         <v>41730</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="Q12" s="3" t="n">
         <v>41730</v>
       </c>
       <c r="R12" t="inlineStr">
@@ -1509,6 +1530,7 @@
           <t>25福保障計第1898号</t>
         </is>
       </c>
+      <c r="S12" s="1" t="n"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
@@ -1526,27 +1548,28 @@
       <c r="Y12" t="n">
         <v>50204</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>有効期限到来により失効（～令和２年４月１日）</t>
         </is>
       </c>
+      <c r="AA12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>3-10</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>7294150</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1367294150</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1561,7 +1584,7 @@
           <t>193-0844</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1581,12 +1604,12 @@
           <t>医療法人財団青溪会</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>193-8505</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>東京都八王子市裏高尾町２７３</t>
         </is>
@@ -1597,7 +1620,7 @@
       <c r="P13" t="n">
         <v>41730</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="Q13" s="3" t="n">
         <v>41730</v>
       </c>
       <c r="R13" t="inlineStr">
@@ -1627,22 +1650,24 @@
       <c r="X13" t="n">
         <v>42604</v>
       </c>
+      <c r="Z13" s="1" t="n"/>
+      <c r="AA13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>3-11</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="2" t="n">
         <v>7294259</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1367294259</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1652,7 +1677,7 @@
           <t>あわーず東京八王子訪問看護リハビリステーション</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>192-0062</t>
         </is>
@@ -1667,7 +1692,7 @@
           <t>八王子市大横町１１－４　ＴＫビル１階</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>050-6865-5000</t>
         </is>
@@ -1693,7 +1718,7 @@
       <c r="P14" t="n">
         <v>41852</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="Q14" s="3" t="n">
         <v>41852</v>
       </c>
       <c r="R14" t="inlineStr">
@@ -1744,12 +1769,12 @@
       <c r="D15" t="n">
         <v>7295041</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1367295041</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1800,7 +1825,7 @@
       <c r="P15" t="n">
         <v>42278</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="Q15" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="R15" t="inlineStr">
@@ -1840,12 +1865,12 @@
       <c r="D16" t="n">
         <v>7295579</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1367295579</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1896,7 +1921,7 @@
       <c r="P16" t="n">
         <v>42278</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="Q16" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="R16" t="inlineStr">
@@ -1948,15 +1973,15 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>7296221</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1367296221</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2007,7 +2032,7 @@
       <c r="P17" t="n">
         <v>42461</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="Q17" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="R17" t="inlineStr">
@@ -2044,15 +2069,15 @@
           <t>3-15</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>7491848</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1367491848</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2103,7 +2128,7 @@
       <c r="P18" t="n">
         <v>42644</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="Q18" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="R18" t="inlineStr">
@@ -2111,7 +2136,7 @@
           <t>28八福障収第476号</t>
         </is>
       </c>
-      <c r="S18" s="1" t="n">
+      <c r="S18" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="T18" t="inlineStr">
@@ -2160,15 +2185,15 @@
           <t>3-16</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="2" t="n">
         <v>7391543</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1367391543</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2219,7 +2244,7 @@
       <c r="P19" t="n">
         <v>43374</v>
       </c>
-      <c r="Q19" s="1" t="n">
+      <c r="Q19" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="R19" t="inlineStr">
@@ -2227,7 +2252,7 @@
           <t>30八福障収第325号</t>
         </is>
       </c>
-      <c r="S19" s="1" t="n">
+      <c r="S19" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="U19" t="inlineStr">
@@ -2261,15 +2286,15 @@
           <t>3-17</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="2" t="n">
         <v>7392228</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1367392228</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2320,7 +2345,7 @@
       <c r="P20" t="n">
         <v>43374</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="Q20" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="R20" t="inlineStr">
@@ -2328,7 +2353,7 @@
           <t>30八福障収第679号</t>
         </is>
       </c>
-      <c r="S20" s="1" t="n">
+      <c r="S20" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="U20" t="inlineStr">
@@ -2357,15 +2382,15 @@
           <t>3-18</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="2" t="n">
         <v>7297781</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1367297781</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2416,7 +2441,7 @@
       <c r="P21" t="n">
         <v>43556</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="Q21" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="R21" t="inlineStr">
@@ -2424,7 +2449,7 @@
           <t>30八福障収第2374号</t>
         </is>
       </c>
-      <c r="S21" s="1" t="n">
+      <c r="S21" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="T21" t="inlineStr">
@@ -2453,15 +2478,15 @@
           <t>3-19</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>7393325</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1367393325</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2516,7 +2541,7 @@
           <t>令和元年10月1日</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>令和元年10月1日</t>
         </is>
@@ -2526,7 +2551,7 @@
           <t>31八福障収第498号</t>
         </is>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="S22" s="4" t="n">
         <v>45931</v>
       </c>
       <c r="T22" t="inlineStr">
@@ -2555,15 +2580,15 @@
           <t>3-20</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="2" t="n">
         <v>7394067</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1367394067</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2614,7 +2639,7 @@
       <c r="P23" t="n">
         <v>44013</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="Q23" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="R23" t="inlineStr">
@@ -2646,12 +2671,12 @@
       <c r="D24" t="n">
         <v>7395072</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1367395072</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2702,7 +2727,7 @@
       <c r="P24" t="n">
         <v>44105</v>
       </c>
-      <c r="Q24" s="1" t="n">
+      <c r="Q24" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="R24" t="inlineStr">
@@ -2731,20 +2756,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>3-22</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="2" t="n">
         <v>7398167</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1367398167</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2795,7 +2820,7 @@
       <c r="P25" t="n">
         <v>44652</v>
       </c>
-      <c r="Q25" s="1" t="n">
+      <c r="Q25" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="R25" t="inlineStr">
@@ -2824,20 +2849,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>3-23</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2" t="n">
         <v>7397748</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1367397748</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2888,7 +2913,7 @@
       <c r="P26" t="n">
         <v>44743</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="Q26" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="R26" t="inlineStr">
@@ -2912,19 +2937,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>3-24</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="2" t="n">
         <v>7398621</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1367398621</t>
         </is>
       </c>
+      <c r="F27" s="2" t="n"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>わかちな訪問看護ステーション</t>
@@ -2995,19 +3021,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>3-25</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="2" t="n">
         <v>7398878</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1367398878</t>
         </is>
       </c>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>指定訪問看護アットリハ八王子</t>
@@ -3083,7 +3110,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>3-26</t>
         </is>
@@ -3166,7 +3193,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>3-27</t>
         </is>
@@ -3260,7 +3287,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>3-28</t>
         </is>
@@ -3343,7 +3370,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>3-29</t>
         </is>
@@ -3381,7 +3408,7 @@
           <t>042-634-9660</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>ビレッジ・エイド株式会社</t>
         </is>
@@ -3391,7 +3418,7 @@
           <t>177-0044</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>練馬区上石神井1-39-4</t>
         </is>
@@ -3426,7 +3453,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>3-30</t>
         </is>
@@ -3464,7 +3491,7 @@
           <t>042-673-6471</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>ＲＥＲＩＳＥ株式会社</t>
         </is>
@@ -3474,7 +3501,7 @@
           <t>193-0826</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>八王子市元八王子町2-2020-24</t>
         </is>
@@ -3509,7 +3536,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>3-31</t>
         </is>
@@ -3547,7 +3574,7 @@
           <t>042-689-4066</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>株式会社Ｗｅｌｌｓｈｉｐ</t>
         </is>
@@ -3557,7 +3584,7 @@
           <t>192-0372</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>八王子市下柚木2-13-5</t>
         </is>
@@ -3592,7 +3619,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>3-32</t>
         </is>
@@ -3635,7 +3662,7 @@
           <t>042-699-0921</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>一般社団法人アルデバラン</t>
         </is>
@@ -3645,7 +3672,7 @@
           <t>192-0914</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>八王子市片倉町1395-26</t>
         </is>
@@ -3688,7 +3715,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>3-33</t>
         </is>
@@ -3726,7 +3753,7 @@
           <t>042-615-4695</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>株式会社一縁</t>
         </is>
@@ -3736,7 +3763,7 @@
           <t>192-0045</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>八王子市大和田町７－１７－１６</t>
         </is>
@@ -3771,7 +3798,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>3-34</t>
         </is>
@@ -3814,7 +3841,7 @@
           <t>042-641-1128</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>株式会社ステア</t>
         </is>
@@ -3824,7 +3851,7 @@
           <t>193-0802</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>八王子市犬目町９１８―１　ロイヤルレジデンス１階１０１号室</t>
         </is>
@@ -3867,7 +3894,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>3-35</t>
         </is>
@@ -3905,7 +3932,7 @@
           <t>042-641-1128</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>株式会社ステア</t>
         </is>
@@ -3915,7 +3942,7 @@
           <t>193-0802</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>八王子市犬目町９１８―１　ロイヤルレジデンス１階１０１号室</t>
         </is>
@@ -3950,7 +3977,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>3-36</t>
         </is>
@@ -3988,7 +4015,7 @@
           <t>042-634-9512</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>株式会社Ring with</t>
         </is>
@@ -3998,7 +4025,7 @@
           <t>547-0035</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>大阪府大阪市平野区西脇１-9-1　西脇一丁目ビル3F</t>
         </is>
@@ -4033,7 +4060,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>3-37</t>
         </is>
@@ -4071,7 +4098,7 @@
           <t>042-683-2172</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>株式会社リベルケア</t>
         </is>
@@ -4081,7 +4108,7 @@
           <t>450-0002</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>愛知県名古屋市中村区名駅３－２８－１２</t>
         </is>
@@ -4121,7 +4148,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>3-38</t>
         </is>
@@ -4159,7 +4186,7 @@
           <t>042-649-5467</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>株式会社クラエ</t>
         </is>
@@ -4169,7 +4196,7 @@
           <t>252-0344</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>神奈川県相模原市南区古淵２丁目３－２０　スアイナーカーウ３０３</t>
         </is>
@@ -4204,7 +4231,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>3-39</t>
         </is>
@@ -4242,7 +4269,7 @@
           <t>042-686-0505</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>ＲＥＲＩＳＥ株式会社</t>
         </is>
@@ -4252,7 +4279,7 @@
           <t>193-0826</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>八王子市元八王子町2-2020-24</t>
         </is>

--- a/data/hachioji_kousei_houkan.xlsx
+++ b/data/hachioji_kousei_houkan.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H.H\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h_hyakutake\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01006B9E-ED07-4A0E-8889-35D84815F24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9071129-E381-47B5-BC7F-196E0D2BBDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" xr2:uid="{E030DF6D-0D80-48DB-A88A-CEC2E7260F0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{86259FA6-9C5B-4814-B1BC-AE275478C609}"/>
   </bookViews>
   <sheets>
     <sheet name="訪問看護" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">訪問看護!$A$3:$AD$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">訪問看護!$A$1:$AE$44</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">訪問看護!$2:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">訪問看護!$A$3:$AF$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,43 +30,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>🐇usagi🐇</author>
-  </authors>
-  <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{9BBAB5C5-EEFD-4CDD-A323-21EAEBE2DEE7}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">数式要修正
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="394">
-  <si>
-    <t>指定自立支援医療機関（育成・更生医療）指定一覧【訪問看護事業者等】（令和8年6月1日現在）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="398">
+  <si>
+    <t>指定自立支援医療機関（育成・更生医療）指定一覧【訪問看護事業者等】（令和8年7月1日現在）</t>
     <rPh sb="0" eb="2">
       <t>シテイ</t>
     </rPh>
@@ -1692,6 +1663,22 @@
     <t>3-11</t>
   </si>
   <si>
+    <t>変更（開設者住所）、更新</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カイセツシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
     <t>あわーず東京八王子訪問看護リハビリステーション</t>
     <rPh sb="4" eb="6">
       <t>トウキョウ</t>
@@ -1784,26 +1771,8 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>2八福障収第228号</t>
-    <rPh sb="1" eb="2">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ショウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ゴウ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
+    <t>8八福障第1893号</t>
+    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>変更届（訪看名称（アワーズ東京訪問看護リハビリステーション(コード変更なし)→、所在地（八王子市千人町１－７－１４→、法人名（株式会社医療看護介護リハビリ生活総合サービスステーション、法人所在地（新宿区住吉町１５－２５）、～令和元年12月1日）</t>
@@ -1852,7 +1821,7 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>変更届（開設者氏名：代表取締役　　岸元悟→代表取締役　本多　克行、令和8年4月1日）</t>
+    <t>変更届（開設者氏名：代表取締役　　岸本悟→代表取締役　本多　克行、令和8年4月1日）</t>
     <rPh sb="10" eb="15">
       <t>ダイヒョウトリシマリヤク</t>
     </rPh>
@@ -1870,6 +1839,25 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>カツユキ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>変更届（開設者住所：新宿区西新宿８丁目３番３２号→新宿区百人町1-22-3新宿ナショナルコート203号、令和7年4月1日）</t>
+    <rPh sb="7" eb="9">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>シンジュクク</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ヒャクニンチョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シンジュク</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ゴウ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -2947,6 +2935,17 @@
     <t>3-20</t>
   </si>
   <si>
+    <t>失効</t>
+    <rPh sb="0" eb="2">
+      <t>シッコウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
     <t>訪問看護ステーション　日なたぼっこ</t>
     <rPh sb="0" eb="4">
       <t>ホウモンカンゴ</t>
@@ -3016,6 +3015,10 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
+    <t>有効期限到来により失効（～令和８年６月３０日）</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
     <t>3-21</t>
   </si>
   <si>
@@ -3887,10 +3890,6 @@
   </si>
   <si>
     <t>3-32</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>〇</t>
     <phoneticPr fontId="5"/>
   </si>
   <si>
@@ -4114,7 +4113,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -4335,11 +4334,11 @@
     <numFmt numFmtId="177" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="178" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@" x16r2:formatCode16="[$-ja-JP-x-gannen]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4347,7 +4346,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4366,7 +4365,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4386,7 +4385,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4406,14 +4405,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4422,13 +4421,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -4477,7 +4469,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -4520,26 +4512,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -4615,6 +4587,17 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -4670,7 +4653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4731,15 +4714,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4758,16 +4744,16 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4776,76 +4762,76 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -5055,7 +5041,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5073,7 +5059,7 @@
     <xf numFmtId="58" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5106,7 +5092,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{2A899044-38EF-4AEA-9ED1-A7CF9AE7C9A1}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{0D787BBE-D92C-4738-9838-B705710A69B4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5122,9 +5108,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5132,44 +5118,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -5197,31 +5183,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -5249,26 +5218,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5277,201 +5229,205 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02398B00-DC8A-4AA5-BF0B-5E73BD9286B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104C0C28-9CCF-4D65-A250-99DFC868D092}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE42"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="11.25" style="142" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.25" style="142" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.9140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="8.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="5.75" customWidth="1"/>
-    <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="32.4140625" customWidth="1"/>
-    <col min="11" max="11" width="8.25" customWidth="1"/>
-    <col min="12" max="12" width="24.6640625" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="8.25" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="32.4140625" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="16.4140625" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="15.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="8.1640625" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="27" style="143" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="28" width="27" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="31" width="27.83203125" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="33" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="143" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="9" style="143" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="9.5" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="29.125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="6.25" customWidth="1"/>
+    <col min="9" max="9" width="7.375" customWidth="1"/>
+    <col min="10" max="10" width="35.375" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="26.875" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="35.375" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="17.875" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="8.875" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="29.5" style="144" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="28" width="29.5" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="31" width="30.375" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="33" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="49.5" customHeight="1">
+    <row r="1" spans="1:31" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5507,7 +5463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" customHeight="1">
+    <row r="2" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -5526,214 +5482,214 @@
       <c r="H2" s="19"/>
       <c r="I2" s="19"/>
       <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="20"/>
+      <c r="L2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="23" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="S2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="T2" s="27" t="s">
         <v>10</v>
       </c>
       <c r="U2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="V2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="W2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="X2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="Y2" s="28" t="s">
+      <c r="Y2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="Z2" s="25" t="s">
+      <c r="Z2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AA2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="25" t="s">
+      <c r="AB2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="25" t="s">
+      <c r="AC2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AD2" s="25" t="s">
+      <c r="AD2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AE2" s="25" t="s">
+      <c r="AE2" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="30" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31" t="s">
+    <row r="3" spans="1:31" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="40" t="s">
+      <c r="O3" s="40"/>
+      <c r="P3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42"/>
     </row>
-    <row r="4" spans="1:31" ht="27.75" customHeight="1" thickTop="1">
-      <c r="A4" s="45" t="s">
+    <row r="4" spans="1:31" ht="27.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="47">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48">
         <v>7191778</v>
       </c>
-      <c r="E4" s="48" t="str">
+      <c r="E4" s="49" t="str">
         <f>"136"&amp;D4</f>
         <v>1367191778</v>
       </c>
-      <c r="F4" s="49" t="str">
+      <c r="F4" s="50" t="str">
         <f>IF(E4=E3,"二重","　")</f>
         <v>　</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="50" t="s">
+      <c r="J4" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="50" t="s">
+      <c r="K4" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="50" t="s">
+      <c r="L4" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M4" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="53">
+      <c r="O4" s="54">
         <v>40137</v>
       </c>
-      <c r="P4" s="54">
+      <c r="P4" s="55">
         <v>40210</v>
       </c>
-      <c r="Q4" s="55">
+      <c r="Q4" s="56">
         <v>40210</v>
       </c>
-      <c r="R4" s="56" t="s">
+      <c r="R4" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="53">
+      <c r="S4" s="54">
         <v>44593</v>
       </c>
-      <c r="T4" s="46" t="s">
+      <c r="T4" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="57" t="s">
+      <c r="U4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="V4" s="58">
+      <c r="V4" s="59">
         <v>1</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="59">
         <v>1</v>
       </c>
-      <c r="X4" s="58">
+      <c r="X4" s="59">
         <v>42202</v>
       </c>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="59"/>
-      <c r="AD4" s="59"/>
-      <c r="AE4" s="59"/>
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
     </row>
-    <row r="5" spans="1:31" ht="91">
-      <c r="A5" s="60" t="s">
+    <row r="5" spans="1:31" ht="94.5" x14ac:dyDescent="0.15">
+      <c r="A5" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63">
+      <c r="B5" s="62"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="64">
         <v>7399256</v>
       </c>
-      <c r="E5" s="49" t="str">
+      <c r="E5" s="50" t="str">
         <f t="shared" ref="E5:E42" si="0">"136"&amp;D5</f>
         <v>1367399256</v>
       </c>
-      <c r="F5" s="49" t="str">
+      <c r="F5" s="50" t="str">
         <f t="shared" ref="F5:F26" si="1">IF(E5=E4,"二重","　")</f>
         <v>　</v>
       </c>
@@ -5743,7 +5699,7 @@
       <c r="H5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="14" t="s">
@@ -5755,47 +5711,47 @@
       <c r="L5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="65" t="s">
+      <c r="M5" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="65" t="s">
+      <c r="N5" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="66">
+      <c r="O5" s="67">
         <v>39106</v>
       </c>
-      <c r="P5" s="66">
+      <c r="P5" s="67">
         <v>38808</v>
       </c>
-      <c r="Q5" s="67">
+      <c r="Q5" s="68">
         <v>39114</v>
       </c>
-      <c r="R5" s="68" t="s">
+      <c r="R5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="66">
+      <c r="S5" s="67">
         <v>45658</v>
       </c>
-      <c r="T5" s="62" t="s">
+      <c r="T5" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="U5" s="69" t="s">
+      <c r="U5" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="70">
+      <c r="V5" s="71">
         <v>1</v>
       </c>
-      <c r="W5" s="70">
+      <c r="W5" s="71">
         <v>1</v>
       </c>
-      <c r="X5" s="70">
+      <c r="X5" s="71">
         <v>41902</v>
       </c>
-      <c r="Y5" s="70"/>
+      <c r="Y5" s="71"/>
       <c r="Z5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AA5" s="71" t="s">
+      <c r="AA5" s="72" t="s">
         <v>56</v>
       </c>
       <c r="AB5" s="14" t="s">
@@ -5811,20 +5767,20 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="78">
-      <c r="A6" s="60" t="s">
+    <row r="6" spans="1:31" ht="81" x14ac:dyDescent="0.15">
+      <c r="A6" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="63">
+      <c r="B6" s="62"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="64">
         <v>7192552</v>
       </c>
-      <c r="E6" s="49" t="str">
+      <c r="E6" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367192552</v>
       </c>
-      <c r="F6" s="49" t="str">
+      <c r="F6" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
@@ -5834,7 +5790,7 @@
       <c r="H6" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="64" t="s">
+      <c r="I6" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="14" t="s">
@@ -5846,43 +5802,43 @@
       <c r="L6" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="65" t="s">
+      <c r="M6" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="65" t="s">
+      <c r="N6" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="O6" s="66">
+      <c r="O6" s="67">
         <v>39093</v>
       </c>
-      <c r="P6" s="66">
+      <c r="P6" s="67">
         <v>38808</v>
       </c>
-      <c r="Q6" s="67">
+      <c r="Q6" s="68">
         <v>39114</v>
       </c>
-      <c r="R6" s="72" t="s">
+      <c r="R6" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="S6" s="66">
+      <c r="S6" s="67">
         <v>45658</v>
       </c>
-      <c r="T6" s="62" t="s">
+      <c r="T6" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="U6" s="69" t="s">
+      <c r="U6" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="70">
+      <c r="V6" s="71">
         <v>1</v>
       </c>
-      <c r="W6" s="70">
+      <c r="W6" s="71">
         <v>1</v>
       </c>
-      <c r="X6" s="70">
+      <c r="X6" s="71">
         <v>41902</v>
       </c>
-      <c r="Y6" s="70"/>
+      <c r="Y6" s="71"/>
       <c r="Z6" s="14" t="s">
         <v>69</v>
       </c>
@@ -5893,35 +5849,35 @@
         <v>71</v>
       </c>
       <c r="AC6" s="14"/>
-      <c r="AD6" s="73"/>
-      <c r="AE6" s="73"/>
+      <c r="AD6" s="74"/>
+      <c r="AE6" s="74"/>
     </row>
-    <row r="7" spans="1:31" ht="26">
-      <c r="A7" s="60" t="s">
+    <row r="7" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A7" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="68" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="64">
         <v>7198534</v>
       </c>
-      <c r="E7" s="49" t="str">
+      <c r="E7" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367198534</v>
       </c>
-      <c r="F7" s="49" t="str">
+      <c r="F7" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="14" t="s">
@@ -5933,35 +5889,35 @@
       <c r="L7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="75">
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="76">
         <v>39350</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="76">
         <v>39417</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="68">
         <v>39417</v>
       </c>
-      <c r="R7" s="72" t="s">
+      <c r="R7" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="S7" s="69"/>
-      <c r="T7" s="68"/>
-      <c r="U7" s="69" t="s">
+      <c r="S7" s="70"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="V7" s="70">
+      <c r="V7" s="71">
         <v>1</v>
       </c>
-      <c r="W7" s="70">
+      <c r="W7" s="71">
         <v>1</v>
       </c>
-      <c r="X7" s="70">
+      <c r="X7" s="71">
         <v>41912</v>
       </c>
-      <c r="Y7" s="70">
+      <c r="Y7" s="71">
         <v>42511</v>
       </c>
       <c r="Z7" s="14" t="s">
@@ -5969,26 +5925,26 @@
       </c>
       <c r="AA7" s="14"/>
       <c r="AB7" s="14"/>
-      <c r="AC7" s="73"/>
-      <c r="AD7" s="73"/>
-      <c r="AE7" s="73"/>
+      <c r="AC7" s="74"/>
+      <c r="AD7" s="74"/>
+      <c r="AE7" s="74"/>
     </row>
-    <row r="8" spans="1:31" ht="26">
-      <c r="A8" s="60" t="s">
+    <row r="8" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A8" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="62" t="s">
+      <c r="B8" s="71"/>
+      <c r="C8" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="64">
         <v>7198997</v>
       </c>
-      <c r="E8" s="49" t="str">
+      <c r="E8" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367198997</v>
       </c>
-      <c r="F8" s="49" t="str">
+      <c r="F8" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
@@ -5998,10 +5954,10 @@
       <c r="H8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="74" t="s">
+      <c r="J8" s="75" t="s">
         <v>84</v>
       </c>
       <c r="K8" s="14" t="s">
@@ -6010,35 +5966,35 @@
       <c r="L8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="75">
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="76">
         <v>39708</v>
       </c>
-      <c r="P8" s="75">
+      <c r="P8" s="76">
         <v>39783</v>
       </c>
-      <c r="Q8" s="76">
+      <c r="Q8" s="77">
         <v>39783</v>
       </c>
-      <c r="R8" s="72" t="s">
+      <c r="R8" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="S8" s="68"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="69" t="s">
+      <c r="S8" s="69"/>
+      <c r="T8" s="69"/>
+      <c r="U8" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="V8" s="70">
+      <c r="V8" s="71">
         <v>1</v>
       </c>
-      <c r="W8" s="70">
+      <c r="W8" s="71">
         <v>1</v>
       </c>
-      <c r="X8" s="77">
+      <c r="X8" s="78">
         <v>42012</v>
       </c>
-      <c r="Y8" s="70">
+      <c r="Y8" s="71">
         <v>42307</v>
       </c>
       <c r="Z8" s="14" t="s">
@@ -6046,34 +6002,34 @@
       </c>
       <c r="AA8" s="14"/>
       <c r="AB8" s="14"/>
-      <c r="AC8" s="73"/>
-      <c r="AD8" s="73"/>
-      <c r="AE8" s="73"/>
+      <c r="AC8" s="74"/>
+      <c r="AD8" s="74"/>
+      <c r="AE8" s="74"/>
     </row>
-    <row r="9" spans="1:31" ht="26">
-      <c r="A9" s="60" t="s">
+    <row r="9" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="78">
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="79">
         <v>7199839</v>
       </c>
-      <c r="E9" s="49" t="str">
+      <c r="E9" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367199839</v>
       </c>
-      <c r="F9" s="49" t="str">
+      <c r="F9" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -6085,66 +6041,66 @@
       <c r="L9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="M9" s="79" t="s">
+      <c r="M9" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="79" t="s">
+      <c r="N9" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="66">
+      <c r="O9" s="67">
         <v>40137</v>
       </c>
-      <c r="P9" s="66">
+      <c r="P9" s="67">
         <v>40210</v>
       </c>
-      <c r="Q9" s="67">
+      <c r="Q9" s="68">
         <v>40210</v>
       </c>
-      <c r="R9" s="72" t="s">
+      <c r="R9" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="S9" s="66">
+      <c r="S9" s="67">
         <v>44593</v>
       </c>
-      <c r="T9" s="62" t="s">
+      <c r="T9" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="U9" s="69" t="s">
+      <c r="U9" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="70">
+      <c r="V9" s="71">
         <v>1</v>
       </c>
-      <c r="W9" s="70">
+      <c r="W9" s="71">
         <v>1</v>
       </c>
-      <c r="X9" s="70">
+      <c r="X9" s="71">
         <v>42202</v>
       </c>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="73"/>
-      <c r="AD9" s="73"/>
-      <c r="AE9" s="73"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="61"/>
+      <c r="AB9" s="61"/>
+      <c r="AC9" s="74"/>
+      <c r="AD9" s="74"/>
+      <c r="AE9" s="74"/>
     </row>
-    <row r="10" spans="1:31" ht="26">
-      <c r="A10" s="60" t="s">
+    <row r="10" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="82">
         <v>7292923</v>
       </c>
-      <c r="E10" s="49" t="str">
+      <c r="E10" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367292923</v>
       </c>
-      <c r="F10" s="49" t="str">
+      <c r="F10" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
@@ -6166,147 +6122,147 @@
       <c r="L10" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="M10" s="65"/>
-      <c r="N10" s="65" t="s">
+      <c r="M10" s="66"/>
+      <c r="N10" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="O10" s="75">
+      <c r="O10" s="76">
         <v>41388</v>
       </c>
-      <c r="P10" s="82">
+      <c r="P10" s="83">
         <v>41487</v>
       </c>
-      <c r="Q10" s="83">
+      <c r="Q10" s="84">
         <v>41487</v>
       </c>
-      <c r="R10" s="84" t="s">
+      <c r="R10" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="S10" s="85"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="68" t="s">
+      <c r="S10" s="86"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70">
+      <c r="V10" s="71"/>
+      <c r="W10" s="71">
         <v>1</v>
       </c>
-      <c r="X10" s="70">
+      <c r="X10" s="71">
         <v>42508</v>
       </c>
-      <c r="Y10" s="70">
+      <c r="Y10" s="71">
         <v>42904</v>
       </c>
-      <c r="Z10" s="86" t="s">
+      <c r="Z10" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="AA10" s="87" t="s">
+      <c r="AA10" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="AB10" s="87"/>
-      <c r="AC10" s="73"/>
-      <c r="AD10" s="73"/>
-      <c r="AE10" s="73"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="74"/>
+      <c r="AD10" s="74"/>
+      <c r="AE10" s="74"/>
     </row>
-    <row r="11" spans="1:31" ht="39">
-      <c r="A11" s="60" t="s">
+    <row r="11" spans="1:31" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="81"/>
+      <c r="C11" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="89">
         <v>7293095</v>
       </c>
-      <c r="E11" s="49" t="str">
+      <c r="E11" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367293095</v>
       </c>
-      <c r="F11" s="49" t="str">
+      <c r="F11" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
-      <c r="G11" s="89" t="s">
+      <c r="G11" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="90" t="s">
+      <c r="I11" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="89" t="s">
+      <c r="J11" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="89" t="s">
+      <c r="K11" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="89" t="s">
+      <c r="L11" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="M11" s="91" t="s">
+      <c r="M11" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="N11" s="92" t="s">
+      <c r="N11" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="93">
+      <c r="O11" s="94">
         <v>41465</v>
       </c>
-      <c r="P11" s="93">
+      <c r="P11" s="94">
         <v>41548</v>
       </c>
-      <c r="Q11" s="94">
+      <c r="Q11" s="95">
         <v>41548</v>
       </c>
-      <c r="R11" s="95" t="s">
+      <c r="R11" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="S11" s="95"/>
-      <c r="T11" s="84"/>
-      <c r="U11" s="72" t="s">
+      <c r="S11" s="96"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="V11" s="70">
+      <c r="V11" s="71">
         <v>1</v>
       </c>
-      <c r="W11" s="70">
+      <c r="W11" s="71">
         <v>1</v>
       </c>
-      <c r="X11" s="70">
+      <c r="X11" s="71">
         <v>42510</v>
       </c>
-      <c r="Y11" s="96">
+      <c r="Y11" s="97">
         <v>42904</v>
       </c>
-      <c r="Z11" s="89" t="s">
+      <c r="Z11" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="AA11" s="87" t="s">
+      <c r="AA11" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="AB11" s="80"/>
-      <c r="AC11" s="73"/>
-      <c r="AD11" s="73"/>
-      <c r="AE11" s="73"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="74"/>
+      <c r="AD11" s="74"/>
+      <c r="AE11" s="74"/>
     </row>
-    <row r="12" spans="1:31" ht="26">
-      <c r="A12" s="60" t="s">
+    <row r="12" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A12" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="71"/>
+      <c r="C12" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="64">
         <v>7293707</v>
       </c>
-      <c r="E12" s="49" t="str">
+      <c r="E12" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367293707</v>
       </c>
-      <c r="F12" s="49" t="str">
+      <c r="F12" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
@@ -6316,7 +6272,7 @@
       <c r="H12" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -6328,64 +6284,64 @@
       <c r="L12" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="M12" s="97" t="s">
+      <c r="M12" s="98" t="s">
         <v>122</v>
       </c>
-      <c r="N12" s="97" t="s">
+      <c r="N12" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="O12" s="66">
+      <c r="O12" s="67">
         <v>41667</v>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="67">
         <v>41730</v>
       </c>
-      <c r="Q12" s="67">
+      <c r="Q12" s="68">
         <v>41730</v>
       </c>
-      <c r="R12" s="62" t="s">
+      <c r="R12" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="S12" s="98"/>
-      <c r="T12" s="99"/>
-      <c r="U12" s="100" t="s">
+      <c r="S12" s="99"/>
+      <c r="T12" s="100"/>
+      <c r="U12" s="101" t="s">
         <v>125</v>
       </c>
-      <c r="V12" s="70">
+      <c r="V12" s="71">
         <v>1</v>
       </c>
-      <c r="W12" s="70">
+      <c r="W12" s="71">
         <v>1</v>
       </c>
-      <c r="X12" s="70">
+      <c r="X12" s="71">
         <v>42604</v>
       </c>
-      <c r="Y12" s="70">
+      <c r="Y12" s="71">
         <v>50204</v>
       </c>
-      <c r="Z12" s="86" t="s">
+      <c r="Z12" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="87"/>
-      <c r="AC12" s="73"/>
-      <c r="AD12" s="73"/>
-      <c r="AE12" s="73"/>
+      <c r="AA12" s="102"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="74"/>
+      <c r="AE12" s="74"/>
     </row>
-    <row r="13" spans="1:31" ht="26">
-      <c r="A13" s="60" t="s">
+    <row r="13" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A13" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="70"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63">
+      <c r="B13" s="71"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64">
         <v>7294150</v>
       </c>
-      <c r="E13" s="49" t="str">
+      <c r="E13" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367294150</v>
       </c>
-      <c r="F13" s="49" t="str">
+      <c r="F13" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
@@ -6395,7 +6351,7 @@
       <c r="H13" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="65" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="14" t="s">
@@ -6407,2259 +6363,2271 @@
       <c r="L13" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="M13" s="97" t="s">
+      <c r="M13" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="N13" s="97" t="s">
+      <c r="N13" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="O13" s="66">
+      <c r="O13" s="67">
         <v>41670</v>
       </c>
-      <c r="P13" s="66">
+      <c r="P13" s="67">
         <v>41730</v>
       </c>
-      <c r="Q13" s="67">
+      <c r="Q13" s="68">
         <v>41730</v>
       </c>
-      <c r="R13" s="62" t="s">
+      <c r="R13" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="S13" s="82">
+      <c r="S13" s="83">
         <v>46113</v>
       </c>
-      <c r="T13" s="102" t="s">
+      <c r="T13" s="103" t="s">
         <v>134</v>
       </c>
-      <c r="U13" s="100" t="s">
+      <c r="U13" s="101" t="s">
         <v>125</v>
       </c>
-      <c r="V13" s="70">
+      <c r="V13" s="71">
         <v>1</v>
       </c>
-      <c r="W13" s="70">
+      <c r="W13" s="71">
         <v>1</v>
       </c>
-      <c r="X13" s="70">
+      <c r="X13" s="71">
         <v>42604</v>
       </c>
-      <c r="Y13" s="70"/>
-      <c r="Z13" s="86"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="87"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="73"/>
-      <c r="AE13" s="73"/>
+      <c r="Y13" s="71"/>
+      <c r="Z13" s="87"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="74"/>
+      <c r="AE13" s="74"/>
     </row>
-    <row r="14" spans="1:31" ht="117">
-      <c r="A14" s="60" t="s">
+    <row r="14" spans="1:31" ht="121.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63">
+      <c r="B14" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="64">
         <v>7294259</v>
       </c>
-      <c r="E14" s="49" t="str">
+      <c r="E14" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367294259</v>
       </c>
-      <c r="F14" s="49" t="str">
+      <c r="F14" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="74" t="s">
         <v>137</v>
+      </c>
+      <c r="H14" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>36</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="K14" s="64" t="s">
         <v>139</v>
       </c>
+      <c r="K14" s="65" t="s">
+        <v>140</v>
+      </c>
       <c r="L14" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M14" s="65" t="s">
         <v>141</v>
       </c>
-      <c r="N14" s="65" t="s">
+      <c r="M14" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="O14" s="75">
+      <c r="N14" s="66" t="s">
+        <v>143</v>
+      </c>
+      <c r="O14" s="76">
         <v>41774</v>
       </c>
-      <c r="P14" s="66">
+      <c r="P14" s="67">
         <v>41852</v>
       </c>
-      <c r="Q14" s="67">
+      <c r="Q14" s="68">
         <v>41852</v>
       </c>
-      <c r="R14" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="S14" s="75">
-        <v>44044</v>
-      </c>
-      <c r="T14" s="62" t="s">
+      <c r="R14" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="U14" s="68" t="s">
+      <c r="S14" s="76">
+        <v>46204</v>
+      </c>
+      <c r="T14" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="U14" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="V14" s="70">
+      <c r="V14" s="71">
         <v>1</v>
       </c>
-      <c r="W14" s="70">
+      <c r="W14" s="71">
         <v>1</v>
       </c>
-      <c r="X14" s="70">
+      <c r="X14" s="71">
         <v>42608</v>
       </c>
-      <c r="Y14" s="70"/>
+      <c r="Y14" s="71"/>
       <c r="Z14" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA14" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="73"/>
-      <c r="AD14" s="73"/>
-      <c r="AE14" s="73"/>
+        <v>147</v>
+      </c>
+      <c r="AB14" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="74"/>
+      <c r="AE14" s="74"/>
     </row>
-    <row r="15" spans="1:31" s="109" customFormat="1" ht="26">
-      <c r="A15" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="103">
+    <row r="15" spans="1:31" s="110" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A15" s="104" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="104">
         <v>7295041</v>
       </c>
-      <c r="E15" s="49" t="str">
+      <c r="E15" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367295041</v>
       </c>
-      <c r="F15" s="49" t="str">
+      <c r="F15" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
-      <c r="G15" s="103" t="s">
-        <v>148</v>
-      </c>
-      <c r="H15" s="103" t="s">
-        <v>149</v>
-      </c>
-      <c r="I15" s="103" t="s">
+      <c r="G15" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="104" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="103" t="s">
-        <v>150</v>
-      </c>
-      <c r="K15" s="103" t="s">
-        <v>151</v>
-      </c>
-      <c r="L15" s="103" t="s">
+      <c r="J15" s="104" t="s">
         <v>152</v>
       </c>
-      <c r="M15" s="105" t="s">
+      <c r="K15" s="104" t="s">
         <v>153</v>
       </c>
-      <c r="N15" s="105" t="s">
+      <c r="L15" s="104" t="s">
         <v>154</v>
       </c>
-      <c r="O15" s="106">
+      <c r="M15" s="106" t="s">
+        <v>155</v>
+      </c>
+      <c r="N15" s="106" t="s">
+        <v>156</v>
+      </c>
+      <c r="O15" s="107">
         <v>42247</v>
       </c>
-      <c r="P15" s="106">
+      <c r="P15" s="107">
         <v>42278</v>
       </c>
-      <c r="Q15" s="107">
+      <c r="Q15" s="108">
         <v>42278</v>
       </c>
-      <c r="R15" s="104" t="s">
-        <v>155</v>
-      </c>
-      <c r="S15" s="108">
+      <c r="R15" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="S15" s="109">
         <v>44470</v>
       </c>
-      <c r="T15" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="U15" s="104" t="s">
+      <c r="T15" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="U15" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V15" s="103">
+      <c r="V15" s="104">
         <v>1</v>
       </c>
-      <c r="W15" s="103">
+      <c r="W15" s="104">
         <v>1</v>
       </c>
-      <c r="X15" s="103">
+      <c r="X15" s="104">
         <v>42710</v>
       </c>
-      <c r="Y15" s="103"/>
-      <c r="Z15" s="103"/>
-      <c r="AA15" s="103"/>
-      <c r="AB15" s="103"/>
-      <c r="AC15" s="103"/>
-      <c r="AD15" s="103"/>
-      <c r="AE15" s="103"/>
+      <c r="Y15" s="104"/>
+      <c r="Z15" s="104"/>
+      <c r="AA15" s="104"/>
+      <c r="AB15" s="104"/>
+      <c r="AC15" s="104"/>
+      <c r="AD15" s="104"/>
+      <c r="AE15" s="104"/>
     </row>
-    <row r="16" spans="1:31" s="109" customFormat="1" ht="91">
-      <c r="A16" s="103" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="110"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="103">
+    <row r="16" spans="1:31" s="110" customFormat="1" ht="94.5" x14ac:dyDescent="0.15">
+      <c r="A16" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="111"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="104">
         <v>7295579</v>
       </c>
-      <c r="E16" s="49" t="str">
+      <c r="E16" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367295579</v>
       </c>
-      <c r="F16" s="49" t="str">
+      <c r="F16" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
-      <c r="G16" s="103" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" s="103" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="103" t="s">
+      <c r="G16" s="104" t="s">
+        <v>160</v>
+      </c>
+      <c r="H16" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="103" t="s">
-        <v>160</v>
-      </c>
-      <c r="K16" s="103" t="s">
+      <c r="J16" s="104" t="s">
+        <v>162</v>
+      </c>
+      <c r="K16" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="L16" s="104" t="s">
+        <v>164</v>
+      </c>
+      <c r="M16" s="106" t="s">
         <v>161</v>
       </c>
-      <c r="L16" s="103" t="s">
-        <v>162</v>
-      </c>
-      <c r="M16" s="105" t="s">
-        <v>159</v>
-      </c>
-      <c r="N16" s="105" t="s">
-        <v>163</v>
-      </c>
-      <c r="O16" s="106">
+      <c r="N16" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="O16" s="107">
         <v>42145</v>
       </c>
-      <c r="P16" s="106">
+      <c r="P16" s="107">
         <v>42278</v>
       </c>
-      <c r="Q16" s="107">
+      <c r="Q16" s="108">
         <v>42278</v>
       </c>
-      <c r="R16" s="104" t="s">
-        <v>164</v>
-      </c>
-      <c r="S16" s="108">
+      <c r="R16" s="105" t="s">
+        <v>166</v>
+      </c>
+      <c r="S16" s="109">
         <v>44470</v>
       </c>
-      <c r="T16" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="U16" s="104" t="s">
+      <c r="T16" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="U16" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V16" s="103">
+      <c r="V16" s="104">
         <v>1</v>
       </c>
-      <c r="W16" s="103">
+      <c r="W16" s="104">
         <v>1</v>
       </c>
-      <c r="X16" s="103">
+      <c r="X16" s="104">
         <v>42710</v>
       </c>
-      <c r="Y16" s="103"/>
+      <c r="Y16" s="104"/>
       <c r="Z16" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA16" s="103" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB16" s="103"/>
-      <c r="AC16" s="103"/>
-      <c r="AD16" s="103"/>
-      <c r="AE16" s="103"/>
+        <v>168</v>
+      </c>
+      <c r="AA16" s="104" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB16" s="104"/>
+      <c r="AC16" s="104"/>
+      <c r="AD16" s="104"/>
+      <c r="AE16" s="104"/>
     </row>
-    <row r="17" spans="1:31" ht="26">
-      <c r="A17" s="103" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="24" t="s">
+    <row r="17" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A17" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="112"/>
+      <c r="C17" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="64">
         <v>7296221</v>
       </c>
-      <c r="E17" s="49" t="str">
+      <c r="E17" s="50" t="str">
         <f t="shared" si="0"/>
         <v>1367296221</v>
       </c>
-      <c r="F17" s="49" t="str">
+      <c r="F17" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="I17" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="104" t="s">
+        <v>172</v>
+      </c>
+      <c r="I17" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="K17" s="103" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="K17" s="104" t="s">
+        <v>174</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="M17" s="105" t="s">
-        <v>174</v>
-      </c>
-      <c r="N17" s="105" t="s">
         <v>175</v>
       </c>
-      <c r="O17" s="106">
+      <c r="M17" s="106" t="s">
+        <v>176</v>
+      </c>
+      <c r="N17" s="106" t="s">
+        <v>177</v>
+      </c>
+      <c r="O17" s="107">
         <v>42383</v>
       </c>
-      <c r="P17" s="106">
+      <c r="P17" s="107">
         <v>42461</v>
       </c>
-      <c r="Q17" s="107">
+      <c r="Q17" s="108">
         <v>42461</v>
       </c>
-      <c r="R17" s="104" t="s">
-        <v>176</v>
-      </c>
-      <c r="S17" s="104"/>
-      <c r="T17" s="104"/>
-      <c r="U17" s="104" t="s">
+      <c r="R17" s="105" t="s">
+        <v>178</v>
+      </c>
+      <c r="S17" s="105"/>
+      <c r="T17" s="105"/>
+      <c r="U17" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V17" s="103">
+      <c r="V17" s="104">
         <v>1</v>
       </c>
-      <c r="W17" s="103">
+      <c r="W17" s="104">
         <v>1</v>
       </c>
-      <c r="X17" s="103">
+      <c r="X17" s="104">
         <v>42804</v>
       </c>
-      <c r="Y17" s="103">
+      <c r="Y17" s="104">
         <v>50404</v>
       </c>
-      <c r="Z17" s="103" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA17" s="103"/>
-      <c r="AB17" s="103"/>
-      <c r="AC17" s="73"/>
-      <c r="AD17" s="73"/>
-      <c r="AE17" s="73"/>
+      <c r="Z17" s="104" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA17" s="104"/>
+      <c r="AB17" s="104"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="74"/>
+      <c r="AE17" s="74"/>
     </row>
-    <row r="18" spans="1:31" ht="65">
-      <c r="A18" s="103" t="s">
-        <v>178</v>
-      </c>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="63">
+    <row r="18" spans="1:31" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A18" s="104" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="113"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="64">
         <v>7491848</v>
       </c>
-      <c r="E18" s="114" t="str">
+      <c r="E18" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367491848</v>
       </c>
-      <c r="F18" s="49" t="str">
+      <c r="F18" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" s="103" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="103" t="s">
+        <v>181</v>
+      </c>
+      <c r="H18" s="104" t="s">
+        <v>176</v>
+      </c>
+      <c r="I18" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="K18" s="103" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="K18" s="104" t="s">
+        <v>183</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="M18" s="105" t="s">
-        <v>183</v>
-      </c>
-      <c r="N18" s="105" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="106">
+      <c r="M18" s="106" t="s">
+        <v>185</v>
+      </c>
+      <c r="N18" s="106" t="s">
+        <v>186</v>
+      </c>
+      <c r="O18" s="107">
         <v>42601</v>
       </c>
-      <c r="P18" s="106">
+      <c r="P18" s="107">
         <v>42644</v>
       </c>
-      <c r="Q18" s="107">
+      <c r="Q18" s="108">
         <v>42461</v>
       </c>
-      <c r="R18" s="104" t="s">
-        <v>185</v>
-      </c>
-      <c r="S18" s="115">
+      <c r="R18" s="105" t="s">
+        <v>187</v>
+      </c>
+      <c r="S18" s="116">
         <v>44652</v>
       </c>
-      <c r="T18" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="U18" s="104" t="s">
+      <c r="T18" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="U18" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V18" s="103">
+      <c r="V18" s="104">
         <v>1</v>
       </c>
-      <c r="W18" s="103">
+      <c r="W18" s="104">
         <v>1</v>
       </c>
-      <c r="X18" s="103">
+      <c r="X18" s="104">
         <v>42810</v>
       </c>
-      <c r="Y18" s="103"/>
-      <c r="Z18" s="103" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA18" s="103" t="s">
-        <v>188</v>
-      </c>
-      <c r="AB18" s="103" t="s">
+      <c r="Y18" s="104"/>
+      <c r="Z18" s="104" t="s">
         <v>189</v>
       </c>
-      <c r="AC18" s="103" t="s">
+      <c r="AA18" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="AD18" s="116"/>
-      <c r="AE18" s="116"/>
+      <c r="AB18" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="AC18" s="104" t="s">
+        <v>192</v>
+      </c>
+      <c r="AD18" s="117"/>
+      <c r="AE18" s="117"/>
     </row>
-    <row r="19" spans="1:31" ht="52">
-      <c r="A19" s="103" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="63">
+    <row r="19" spans="1:31" ht="54" x14ac:dyDescent="0.15">
+      <c r="A19" s="104" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="105"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="64">
         <v>7391543</v>
       </c>
-      <c r="E19" s="114" t="str">
+      <c r="E19" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367391543</v>
       </c>
-      <c r="F19" s="49" t="str">
+      <c r="F19" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="H19" s="103" t="s">
-        <v>193</v>
-      </c>
-      <c r="I19" s="103" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" s="104" t="s">
+        <v>195</v>
+      </c>
+      <c r="I19" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="K19" s="103" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" s="104" t="s">
+        <v>197</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="M19" s="106" t="s">
         <v>195</v>
       </c>
-      <c r="L19" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M19" s="105" t="s">
-        <v>193</v>
-      </c>
-      <c r="N19" s="105" t="s">
-        <v>197</v>
-      </c>
-      <c r="O19" s="106">
+      <c r="N19" s="106" t="s">
+        <v>199</v>
+      </c>
+      <c r="O19" s="107">
         <v>43248</v>
       </c>
-      <c r="P19" s="106">
+      <c r="P19" s="107">
         <v>43374</v>
       </c>
-      <c r="Q19" s="107">
+      <c r="Q19" s="108">
         <v>43374</v>
       </c>
-      <c r="R19" s="104" t="s">
-        <v>198</v>
-      </c>
-      <c r="S19" s="115">
+      <c r="R19" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="S19" s="116">
         <v>45566</v>
       </c>
-      <c r="T19" s="104"/>
-      <c r="U19" s="104" t="s">
+      <c r="T19" s="105"/>
+      <c r="U19" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V19" s="103">
+      <c r="V19" s="104">
         <v>1</v>
       </c>
-      <c r="W19" s="103">
+      <c r="W19" s="104">
         <v>1</v>
       </c>
-      <c r="X19" s="103">
+      <c r="X19" s="104">
         <v>43010</v>
       </c>
-      <c r="Y19" s="103"/>
-      <c r="Z19" s="103" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA19" s="103" t="s">
-        <v>200</v>
-      </c>
-      <c r="AB19" s="103"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="73"/>
-      <c r="AE19" s="73"/>
+      <c r="Y19" s="104"/>
+      <c r="Z19" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA19" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB19" s="104"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="74"/>
+      <c r="AE19" s="74"/>
     </row>
-    <row r="20" spans="1:31" ht="26">
-      <c r="A20" s="103" t="s">
-        <v>201</v>
-      </c>
-      <c r="B20" s="104"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="63">
+    <row r="20" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A20" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" s="105"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="64">
         <v>7392228</v>
       </c>
-      <c r="E20" s="114" t="str">
+      <c r="E20" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367392228</v>
       </c>
-      <c r="F20" s="49" t="str">
+      <c r="F20" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="H20" s="103" t="s">
-        <v>203</v>
-      </c>
-      <c r="I20" s="103" t="s">
+        <v>204</v>
+      </c>
+      <c r="H20" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="I20" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="K20" s="103" t="s">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="K20" s="104" t="s">
+        <v>207</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="M20" s="105" t="s">
-        <v>207</v>
-      </c>
-      <c r="N20" s="105" t="s">
         <v>208</v>
       </c>
-      <c r="O20" s="106">
+      <c r="M20" s="106" t="s">
+        <v>209</v>
+      </c>
+      <c r="N20" s="106" t="s">
+        <v>210</v>
+      </c>
+      <c r="O20" s="107">
         <v>43314</v>
       </c>
-      <c r="P20" s="106">
+      <c r="P20" s="107">
         <v>43374</v>
       </c>
-      <c r="Q20" s="107">
+      <c r="Q20" s="108">
         <v>43374</v>
       </c>
-      <c r="R20" s="104" t="s">
-        <v>209</v>
-      </c>
-      <c r="S20" s="115">
+      <c r="R20" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="S20" s="116">
         <v>45566</v>
       </c>
-      <c r="T20" s="104"/>
-      <c r="U20" s="104" t="s">
+      <c r="T20" s="105"/>
+      <c r="U20" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V20" s="103">
+      <c r="V20" s="104">
         <v>1</v>
       </c>
-      <c r="W20" s="103">
+      <c r="W20" s="104">
         <v>1</v>
       </c>
-      <c r="X20" s="103">
+      <c r="X20" s="104">
         <v>43010</v>
       </c>
-      <c r="Y20" s="103"/>
-      <c r="Z20" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="AA20" s="103"/>
-      <c r="AB20" s="103"/>
-      <c r="AC20" s="73"/>
-      <c r="AD20" s="73"/>
-      <c r="AE20" s="73"/>
+      <c r="Y20" s="104"/>
+      <c r="Z20" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA20" s="104"/>
+      <c r="AB20" s="104"/>
+      <c r="AC20" s="74"/>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="74"/>
     </row>
-    <row r="21" spans="1:31" ht="26">
-      <c r="A21" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="B21" s="117"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="63">
+    <row r="21" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A21" s="104" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="118"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="64">
         <v>7297781</v>
       </c>
-      <c r="E21" s="114" t="str">
+      <c r="E21" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367297781</v>
       </c>
-      <c r="F21" s="49" t="str">
+      <c r="F21" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="H21" s="103" t="s">
-        <v>213</v>
-      </c>
-      <c r="I21" s="103" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="104" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="K21" s="103" t="s">
-        <v>215</v>
+        <v>216</v>
+      </c>
+      <c r="K21" s="104" t="s">
+        <v>217</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="M21" s="105" t="s">
-        <v>217</v>
-      </c>
-      <c r="N21" s="105" t="s">
         <v>218</v>
       </c>
-      <c r="O21" s="106">
+      <c r="M21" s="106" t="s">
+        <v>219</v>
+      </c>
+      <c r="N21" s="106" t="s">
+        <v>220</v>
+      </c>
+      <c r="O21" s="107">
         <v>43487</v>
       </c>
-      <c r="P21" s="106">
+      <c r="P21" s="107">
         <v>43556</v>
       </c>
-      <c r="Q21" s="107">
+      <c r="Q21" s="108">
         <v>43556</v>
       </c>
-      <c r="R21" s="104" t="s">
-        <v>219</v>
-      </c>
-      <c r="S21" s="118">
+      <c r="R21" s="105" t="s">
+        <v>221</v>
+      </c>
+      <c r="S21" s="119">
         <v>45748</v>
       </c>
-      <c r="T21" s="104" t="s">
-        <v>220</v>
-      </c>
-      <c r="U21" s="104" t="s">
+      <c r="T21" s="105" t="s">
+        <v>222</v>
+      </c>
+      <c r="U21" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V21" s="103">
+      <c r="V21" s="104">
         <v>1</v>
       </c>
-      <c r="W21" s="103">
+      <c r="W21" s="104">
         <v>1</v>
       </c>
-      <c r="X21" s="103">
+      <c r="X21" s="104">
         <v>43104</v>
       </c>
-      <c r="Y21" s="103"/>
-      <c r="Z21" s="103"/>
-      <c r="AA21" s="103"/>
-      <c r="AB21" s="103"/>
-      <c r="AC21" s="73"/>
-      <c r="AD21" s="73"/>
-      <c r="AE21" s="73"/>
+      <c r="Y21" s="104"/>
+      <c r="Z21" s="104"/>
+      <c r="AA21" s="104"/>
+      <c r="AB21" s="104"/>
+      <c r="AC21" s="74"/>
+      <c r="AD21" s="74"/>
+      <c r="AE21" s="74"/>
     </row>
-    <row r="22" spans="1:31" ht="26">
-      <c r="A22" s="103" t="s">
-        <v>221</v>
-      </c>
-      <c r="B22" s="117"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="63">
+    <row r="22" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A22" s="104" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="118"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="64">
         <v>7393325</v>
       </c>
-      <c r="E22" s="114" t="str">
+      <c r="E22" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367393325</v>
       </c>
-      <c r="F22" s="49" t="str">
+      <c r="F22" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="H22" s="103" t="s">
-        <v>223</v>
-      </c>
-      <c r="I22" s="103" t="s">
+        <v>224</v>
+      </c>
+      <c r="H22" s="104" t="s">
+        <v>225</v>
+      </c>
+      <c r="I22" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="K22" s="103" t="s">
-        <v>225</v>
+        <v>226</v>
+      </c>
+      <c r="K22" s="104" t="s">
+        <v>227</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="M22" s="105" t="s">
-        <v>227</v>
-      </c>
-      <c r="N22" s="105" t="s">
         <v>228</v>
       </c>
-      <c r="O22" s="113" t="s">
+      <c r="M22" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="P22" s="113" t="s">
+      <c r="N22" s="106" t="s">
         <v>230</v>
       </c>
-      <c r="Q22" s="107" t="s">
-        <v>230</v>
-      </c>
-      <c r="R22" s="104" t="s">
+      <c r="O22" s="114" t="s">
         <v>231</v>
       </c>
-      <c r="S22" s="118">
+      <c r="P22" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q22" s="108" t="s">
+        <v>232</v>
+      </c>
+      <c r="R22" s="105" t="s">
+        <v>233</v>
+      </c>
+      <c r="S22" s="119">
         <v>45931</v>
       </c>
-      <c r="T22" s="110" t="s">
-        <v>232</v>
-      </c>
-      <c r="U22" s="104" t="s">
+      <c r="T22" s="111" t="s">
+        <v>234</v>
+      </c>
+      <c r="U22" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V22" s="103">
+      <c r="V22" s="104">
         <v>1</v>
       </c>
-      <c r="W22" s="103">
+      <c r="W22" s="104">
         <v>1</v>
       </c>
-      <c r="X22" s="103">
+      <c r="X22" s="104">
         <v>50110</v>
       </c>
-      <c r="Y22" s="111"/>
-      <c r="Z22" s="103"/>
-      <c r="AA22" s="111"/>
-      <c r="AB22" s="111"/>
-      <c r="AC22" s="73"/>
-      <c r="AD22" s="73"/>
-      <c r="AE22" s="73"/>
+      <c r="Y22" s="112"/>
+      <c r="Z22" s="104"/>
+      <c r="AA22" s="112"/>
+      <c r="AB22" s="112"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="74"/>
     </row>
-    <row r="23" spans="1:31" ht="26">
-      <c r="A23" s="103" t="s">
-        <v>233</v>
-      </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="63">
+    <row r="23" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A23" s="104" t="s">
+        <v>235</v>
+      </c>
+      <c r="B23" s="118" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="64">
         <v>7394067</v>
       </c>
-      <c r="E23" s="114" t="str">
+      <c r="E23" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367394067</v>
       </c>
-      <c r="F23" s="49" t="str">
+      <c r="F23" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H23" s="103" t="s">
-        <v>235</v>
-      </c>
-      <c r="I23" s="103" t="s">
+        <v>238</v>
+      </c>
+      <c r="H23" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="I23" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="K23" s="103" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="K23" s="104" t="s">
+        <v>241</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="M23" s="105" t="s">
-        <v>235</v>
-      </c>
-      <c r="N23" s="105" t="s">
-        <v>236</v>
-      </c>
-      <c r="O23" s="106">
+        <v>242</v>
+      </c>
+      <c r="M23" s="106" t="s">
+        <v>239</v>
+      </c>
+      <c r="N23" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="O23" s="107">
         <v>43936</v>
       </c>
-      <c r="P23" s="106">
+      <c r="P23" s="107">
         <v>44013</v>
       </c>
-      <c r="Q23" s="107">
+      <c r="Q23" s="108">
         <v>44013</v>
       </c>
-      <c r="R23" s="104" t="s">
-        <v>239</v>
-      </c>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="104" t="s">
+      <c r="R23" s="105" t="s">
+        <v>243</v>
+      </c>
+      <c r="S23" s="112"/>
+      <c r="T23" s="112"/>
+      <c r="U23" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V23" s="103">
+      <c r="V23" s="104">
         <v>1</v>
       </c>
-      <c r="W23" s="103">
+      <c r="W23" s="104">
         <v>1</v>
       </c>
-      <c r="X23" s="103">
+      <c r="X23" s="104">
         <v>50207</v>
       </c>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="103"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="111"/>
-      <c r="AC23" s="73"/>
-      <c r="AD23" s="73"/>
-      <c r="AE23" s="73"/>
+      <c r="Y23" s="112">
+        <v>50806</v>
+      </c>
+      <c r="Z23" s="104" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA23" s="112"/>
+      <c r="AB23" s="112"/>
+      <c r="AC23" s="74"/>
+      <c r="AD23" s="74"/>
+      <c r="AE23" s="74"/>
     </row>
-    <row r="24" spans="1:31" ht="52">
-      <c r="A24" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="B24" s="117"/>
-      <c r="C24" s="113"/>
-      <c r="D24" s="111">
+    <row r="24" spans="1:31" ht="54" x14ac:dyDescent="0.15">
+      <c r="A24" s="104" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" s="118"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="112">
         <v>7395072</v>
       </c>
-      <c r="E24" s="114" t="str">
+      <c r="E24" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367395072</v>
       </c>
-      <c r="F24" s="49" t="str">
+      <c r="F24" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
-      <c r="G24" s="103" t="s">
-        <v>241</v>
-      </c>
-      <c r="H24" s="103" t="s">
-        <v>242</v>
-      </c>
-      <c r="I24" s="103" t="s">
+      <c r="G24" s="104" t="s">
+        <v>246</v>
+      </c>
+      <c r="H24" s="104" t="s">
+        <v>247</v>
+      </c>
+      <c r="I24" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J24" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="K24" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="L24" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="M24" s="105" t="s">
-        <v>246</v>
-      </c>
-      <c r="N24" s="105" t="s">
-        <v>247</v>
-      </c>
-      <c r="O24" s="106">
+      <c r="J24" s="112" t="s">
+        <v>248</v>
+      </c>
+      <c r="K24" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="L24" s="112" t="s">
+        <v>250</v>
+      </c>
+      <c r="M24" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="N24" s="106" t="s">
+        <v>252</v>
+      </c>
+      <c r="O24" s="107">
         <v>44055</v>
       </c>
-      <c r="P24" s="106">
+      <c r="P24" s="107">
         <v>44105</v>
       </c>
-      <c r="Q24" s="107">
+      <c r="Q24" s="108">
         <v>44105</v>
       </c>
-      <c r="R24" s="113" t="s">
-        <v>248</v>
-      </c>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="104" t="s">
+      <c r="R24" s="114" t="s">
+        <v>253</v>
+      </c>
+      <c r="S24" s="112"/>
+      <c r="T24" s="112"/>
+      <c r="U24" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V24" s="103">
+      <c r="V24" s="104">
         <v>1</v>
       </c>
-      <c r="W24" s="103">
+      <c r="W24" s="104">
         <v>1</v>
       </c>
-      <c r="X24" s="111">
+      <c r="X24" s="112">
         <v>50210</v>
       </c>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="111"/>
-      <c r="AC24" s="73"/>
-      <c r="AD24" s="73"/>
-      <c r="AE24" s="73"/>
+      <c r="Y24" s="112"/>
+      <c r="Z24" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA24" s="112"/>
+      <c r="AB24" s="112"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="74"/>
+      <c r="AE24" s="74"/>
     </row>
-    <row r="25" spans="1:31" ht="46.5" customHeight="1">
-      <c r="A25" s="119" t="s">
-        <v>250</v>
-      </c>
-      <c r="B25" s="112"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="63">
+    <row r="25" spans="1:31" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="120" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="113"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="64">
         <v>7398167</v>
       </c>
-      <c r="E25" s="114" t="str">
+      <c r="E25" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367398167</v>
       </c>
-      <c r="F25" s="49" t="str">
+      <c r="F25" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="H25" s="103" t="s">
-        <v>252</v>
-      </c>
-      <c r="I25" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="H25" s="104" t="s">
+        <v>257</v>
+      </c>
+      <c r="I25" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="K25" s="103" t="s">
-        <v>254</v>
+        <v>258</v>
+      </c>
+      <c r="K25" s="104" t="s">
+        <v>259</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="M25" s="105" t="s">
-        <v>256</v>
-      </c>
-      <c r="N25" s="105" t="s">
-        <v>257</v>
-      </c>
-      <c r="O25" s="106">
+        <v>260</v>
+      </c>
+      <c r="M25" s="106" t="s">
+        <v>261</v>
+      </c>
+      <c r="N25" s="106" t="s">
+        <v>262</v>
+      </c>
+      <c r="O25" s="107">
         <v>44599</v>
       </c>
-      <c r="P25" s="106">
+      <c r="P25" s="107">
         <v>44652</v>
       </c>
-      <c r="Q25" s="107">
+      <c r="Q25" s="108">
         <v>44652</v>
       </c>
-      <c r="R25" s="104" t="s">
-        <v>258</v>
-      </c>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="104" t="s">
+      <c r="R25" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="S25" s="112"/>
+      <c r="T25" s="112"/>
+      <c r="U25" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V25" s="103">
+      <c r="V25" s="104">
         <v>1</v>
       </c>
-      <c r="W25" s="103">
+      <c r="W25" s="104">
         <v>1</v>
       </c>
-      <c r="X25" s="103">
+      <c r="X25" s="104">
         <v>50404</v>
       </c>
-      <c r="Y25" s="111"/>
+      <c r="Y25" s="112"/>
       <c r="Z25" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA25" s="111"/>
-      <c r="AB25" s="111"/>
-      <c r="AC25" s="73"/>
-      <c r="AD25" s="73"/>
-      <c r="AE25" s="73"/>
+        <v>264</v>
+      </c>
+      <c r="AA25" s="112"/>
+      <c r="AB25" s="112"/>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="74"/>
+      <c r="AE25" s="74"/>
     </row>
-    <row r="26" spans="1:31" ht="26">
-      <c r="A26" s="119" t="s">
-        <v>260</v>
-      </c>
-      <c r="B26" s="117"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="63">
+    <row r="26" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A26" s="120" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="118"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="64">
         <v>7397748</v>
       </c>
-      <c r="E26" s="114" t="str">
+      <c r="E26" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367397748</v>
       </c>
-      <c r="F26" s="49" t="str">
+      <c r="F26" s="50" t="str">
         <f t="shared" si="1"/>
         <v>　</v>
       </c>
       <c r="G26" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="H26" s="104" t="s">
         <v>261</v>
       </c>
-      <c r="H26" s="103" t="s">
-        <v>256</v>
-      </c>
-      <c r="I26" s="103" t="s">
+      <c r="I26" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="K26" s="103" t="s">
-        <v>263</v>
+        <v>267</v>
+      </c>
+      <c r="K26" s="104" t="s">
+        <v>268</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="M26" s="105" t="s">
-        <v>265</v>
-      </c>
-      <c r="N26" s="105" t="s">
-        <v>266</v>
-      </c>
-      <c r="O26" s="106">
+        <v>269</v>
+      </c>
+      <c r="M26" s="106" t="s">
+        <v>270</v>
+      </c>
+      <c r="N26" s="106" t="s">
+        <v>271</v>
+      </c>
+      <c r="O26" s="107">
         <v>44627</v>
       </c>
-      <c r="P26" s="106">
+      <c r="P26" s="107">
         <v>44743</v>
       </c>
-      <c r="Q26" s="107">
+      <c r="Q26" s="108">
         <v>44743</v>
       </c>
-      <c r="R26" s="104" t="s">
-        <v>267</v>
-      </c>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="104" t="s">
+      <c r="R26" s="105" t="s">
+        <v>272</v>
+      </c>
+      <c r="S26" s="112"/>
+      <c r="T26" s="112"/>
+      <c r="U26" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V26" s="103">
+      <c r="V26" s="104">
         <v>1</v>
       </c>
-      <c r="W26" s="103">
+      <c r="W26" s="104">
         <v>1</v>
       </c>
-      <c r="X26" s="103">
+      <c r="X26" s="104">
         <v>50407</v>
       </c>
-      <c r="Y26" s="111"/>
-      <c r="Z26" s="103"/>
-      <c r="AA26" s="111"/>
-      <c r="AB26" s="111"/>
-      <c r="AC26" s="73"/>
-      <c r="AD26" s="73"/>
-      <c r="AE26" s="73"/>
+      <c r="Y26" s="112"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="112"/>
+      <c r="AB26" s="112"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="74"/>
     </row>
-    <row r="27" spans="1:31" ht="26">
-      <c r="A27" s="119" t="s">
-        <v>268</v>
-      </c>
-      <c r="B27" s="117"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="63">
+    <row r="27" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A27" s="120" t="s">
+        <v>273</v>
+      </c>
+      <c r="B27" s="118"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="64">
         <v>7398621</v>
       </c>
-      <c r="E27" s="114" t="str">
+      <c r="E27" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367398621</v>
       </c>
-      <c r="F27" s="49"/>
+      <c r="F27" s="50"/>
       <c r="G27" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="H27" s="103" t="s">
-        <v>270</v>
-      </c>
-      <c r="I27" s="103" t="s">
+        <v>274</v>
+      </c>
+      <c r="H27" s="104" t="s">
+        <v>275</v>
+      </c>
+      <c r="I27" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="K27" s="103" t="s">
-        <v>272</v>
+        <v>276</v>
+      </c>
+      <c r="K27" s="104" t="s">
+        <v>277</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="M27" s="105" t="s">
-        <v>274</v>
-      </c>
-      <c r="N27" s="105" t="s">
-        <v>275</v>
-      </c>
-      <c r="O27" s="106">
+        <v>278</v>
+      </c>
+      <c r="M27" s="106" t="s">
+        <v>279</v>
+      </c>
+      <c r="N27" s="106" t="s">
+        <v>280</v>
+      </c>
+      <c r="O27" s="107">
         <v>44782</v>
       </c>
-      <c r="P27" s="106">
+      <c r="P27" s="107">
         <v>44835</v>
       </c>
-      <c r="Q27" s="106">
+      <c r="Q27" s="107">
         <v>44835</v>
       </c>
-      <c r="R27" s="104" t="s">
-        <v>276</v>
-      </c>
-      <c r="S27" s="111"/>
-      <c r="T27" s="111"/>
-      <c r="U27" s="104" t="s">
+      <c r="R27" s="105" t="s">
+        <v>281</v>
+      </c>
+      <c r="S27" s="112"/>
+      <c r="T27" s="112"/>
+      <c r="U27" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V27" s="103">
+      <c r="V27" s="104">
         <v>1</v>
       </c>
-      <c r="W27" s="103">
+      <c r="W27" s="104">
         <v>1</v>
       </c>
-      <c r="X27" s="103">
+      <c r="X27" s="104">
         <v>50410</v>
       </c>
-      <c r="Y27" s="111"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="111"/>
-      <c r="AB27" s="111"/>
-      <c r="AC27" s="73"/>
-      <c r="AD27" s="73"/>
-      <c r="AE27" s="73"/>
+      <c r="Y27" s="112"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="112"/>
+      <c r="AB27" s="112"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="74"/>
     </row>
-    <row r="28" spans="1:31" ht="78">
-      <c r="A28" s="119" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="117"/>
-      <c r="C28" s="113"/>
-      <c r="D28" s="63">
+    <row r="28" spans="1:31" ht="81" x14ac:dyDescent="0.15">
+      <c r="A28" s="120" t="s">
+        <v>282</v>
+      </c>
+      <c r="B28" s="118"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="64">
         <v>7398878</v>
       </c>
-      <c r="E28" s="114" t="str">
+      <c r="E28" s="115" t="str">
         <f t="shared" si="0"/>
         <v>1367398878</v>
       </c>
-      <c r="F28" s="49"/>
+      <c r="F28" s="50"/>
       <c r="G28" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="H28" s="103" t="s">
-        <v>279</v>
-      </c>
-      <c r="I28" s="103" t="s">
+        <v>283</v>
+      </c>
+      <c r="H28" s="104" t="s">
+        <v>284</v>
+      </c>
+      <c r="I28" s="104" t="s">
         <v>36</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="K28" s="103" t="s">
-        <v>281</v>
+        <v>285</v>
+      </c>
+      <c r="K28" s="104" t="s">
+        <v>286</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="M28" s="105" t="s">
-        <v>283</v>
-      </c>
-      <c r="N28" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="O28" s="106">
+        <v>287</v>
+      </c>
+      <c r="M28" s="106" t="s">
+        <v>288</v>
+      </c>
+      <c r="N28" s="106" t="s">
+        <v>289</v>
+      </c>
+      <c r="O28" s="107">
         <v>44781</v>
       </c>
-      <c r="P28" s="106">
+      <c r="P28" s="107">
         <v>44835</v>
       </c>
-      <c r="Q28" s="106">
+      <c r="Q28" s="107">
         <v>44835</v>
       </c>
-      <c r="R28" s="104" t="s">
-        <v>285</v>
-      </c>
-      <c r="S28" s="111"/>
-      <c r="T28" s="111"/>
-      <c r="U28" s="104" t="s">
+      <c r="R28" s="105" t="s">
+        <v>290</v>
+      </c>
+      <c r="S28" s="112"/>
+      <c r="T28" s="112"/>
+      <c r="U28" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V28" s="103">
+      <c r="V28" s="104">
         <v>1</v>
       </c>
-      <c r="W28" s="103">
+      <c r="W28" s="104">
         <v>1</v>
       </c>
-      <c r="X28" s="103">
+      <c r="X28" s="104">
         <v>50410</v>
       </c>
-      <c r="Y28" s="111"/>
-      <c r="Z28" s="103" t="s">
-        <v>286</v>
-      </c>
-      <c r="AA28" s="111"/>
-      <c r="AB28" s="111"/>
-      <c r="AC28" s="73"/>
-      <c r="AD28" s="73"/>
-      <c r="AE28" s="73"/>
+      <c r="Y28" s="112"/>
+      <c r="Z28" s="104" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA28" s="112"/>
+      <c r="AB28" s="112"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="74"/>
     </row>
-    <row r="29" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A29" s="119" t="s">
-        <v>287</v>
-      </c>
-      <c r="B29" s="120"/>
-      <c r="C29" s="121"/>
-      <c r="D29" s="73">
+    <row r="29" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="120" t="s">
+        <v>292</v>
+      </c>
+      <c r="B29" s="121"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="74">
         <v>7491236</v>
       </c>
-      <c r="E29" s="73" t="str">
+      <c r="E29" s="74" t="str">
         <f t="shared" si="0"/>
         <v>1367491236</v>
       </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="111" t="s">
-        <v>288</v>
-      </c>
-      <c r="H29" s="116" t="s">
-        <v>289</v>
-      </c>
-      <c r="I29" s="103" t="s">
+      <c r="F29" s="74"/>
+      <c r="G29" s="112" t="s">
+        <v>293</v>
+      </c>
+      <c r="H29" s="117" t="s">
+        <v>294</v>
+      </c>
+      <c r="I29" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="103" t="s">
-        <v>290</v>
-      </c>
-      <c r="K29" s="116" t="s">
-        <v>291</v>
-      </c>
-      <c r="L29" s="73" t="s">
-        <v>292</v>
-      </c>
-      <c r="M29" s="122" t="s">
-        <v>293</v>
-      </c>
-      <c r="N29" s="122" t="s">
-        <v>294</v>
-      </c>
-      <c r="O29" s="106">
+      <c r="J29" s="104" t="s">
+        <v>295</v>
+      </c>
+      <c r="K29" s="117" t="s">
+        <v>296</v>
+      </c>
+      <c r="L29" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="M29" s="123" t="s">
+        <v>298</v>
+      </c>
+      <c r="N29" s="123" t="s">
+        <v>299</v>
+      </c>
+      <c r="O29" s="107">
         <v>45054</v>
       </c>
-      <c r="P29" s="123">
+      <c r="P29" s="124">
         <v>45108</v>
       </c>
-      <c r="Q29" s="123">
+      <c r="Q29" s="124">
         <v>45108</v>
       </c>
-      <c r="R29" s="113" t="s">
-        <v>295</v>
-      </c>
-      <c r="S29" s="73"/>
-      <c r="T29" s="73"/>
-      <c r="U29" s="104" t="s">
+      <c r="R29" s="114" t="s">
+        <v>300</v>
+      </c>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
+      <c r="U29" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V29" s="103">
+      <c r="V29" s="104">
         <v>1</v>
       </c>
-      <c r="W29" s="103">
+      <c r="W29" s="104">
         <v>1</v>
       </c>
-      <c r="X29" s="73">
+      <c r="X29" s="74">
         <v>50507</v>
       </c>
-      <c r="Y29" s="73"/>
-      <c r="Z29" s="116"/>
-      <c r="AA29" s="73"/>
-      <c r="AB29" s="73"/>
-      <c r="AC29" s="73"/>
-      <c r="AD29" s="73"/>
-      <c r="AE29" s="73"/>
+      <c r="Y29" s="74"/>
+      <c r="Z29" s="117"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="74"/>
+      <c r="AE29" s="74"/>
     </row>
-    <row r="30" spans="1:31" ht="72">
-      <c r="A30" s="119" t="s">
-        <v>296</v>
-      </c>
-      <c r="B30" s="124" t="s">
-        <v>297</v>
-      </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="125">
+    <row r="30" spans="1:31" ht="54" x14ac:dyDescent="0.15">
+      <c r="A30" s="120" t="s">
+        <v>301</v>
+      </c>
+      <c r="B30" s="125" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="122"/>
+      <c r="D30" s="126">
         <v>7493158</v>
       </c>
-      <c r="E30" s="73" t="str">
+      <c r="E30" s="74" t="str">
         <f t="shared" si="0"/>
         <v>1367493158</v>
       </c>
-      <c r="F30" s="73"/>
-      <c r="G30" s="103" t="s">
-        <v>298</v>
-      </c>
-      <c r="H30" s="116" t="s">
-        <v>299</v>
-      </c>
-      <c r="I30" s="103" t="s">
+      <c r="F30" s="74"/>
+      <c r="G30" s="104" t="s">
+        <v>303</v>
+      </c>
+      <c r="H30" s="117" t="s">
+        <v>304</v>
+      </c>
+      <c r="I30" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="103" t="s">
-        <v>300</v>
-      </c>
-      <c r="K30" s="116" t="s">
-        <v>301</v>
-      </c>
-      <c r="L30" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="M30" s="122" t="s">
-        <v>303</v>
-      </c>
-      <c r="N30" s="122" t="s">
-        <v>304</v>
-      </c>
-      <c r="O30" s="106">
+      <c r="J30" s="104" t="s">
+        <v>305</v>
+      </c>
+      <c r="K30" s="117" t="s">
+        <v>306</v>
+      </c>
+      <c r="L30" s="74" t="s">
+        <v>307</v>
+      </c>
+      <c r="M30" s="123" t="s">
+        <v>308</v>
+      </c>
+      <c r="N30" s="123" t="s">
+        <v>309</v>
+      </c>
+      <c r="O30" s="107">
         <v>45297</v>
       </c>
-      <c r="P30" s="123">
+      <c r="P30" s="124">
         <v>45383</v>
       </c>
-      <c r="Q30" s="123">
+      <c r="Q30" s="124">
         <v>45383</v>
       </c>
-      <c r="R30" s="113" t="s">
-        <v>305</v>
-      </c>
-      <c r="S30" s="116"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="104" t="s">
+      <c r="R30" s="114" t="s">
+        <v>310</v>
+      </c>
+      <c r="S30" s="117"/>
+      <c r="T30" s="74"/>
+      <c r="U30" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V30" s="103">
+      <c r="V30" s="104">
         <v>1</v>
       </c>
-      <c r="W30" s="103">
+      <c r="W30" s="104">
         <v>1</v>
       </c>
-      <c r="X30" s="73">
+      <c r="X30" s="74">
         <v>50604</v>
       </c>
-      <c r="Y30" s="73"/>
-      <c r="Z30" s="116" t="s">
-        <v>306</v>
-      </c>
-      <c r="AA30" s="73"/>
-      <c r="AB30" s="73"/>
-      <c r="AC30" s="73"/>
-      <c r="AD30" s="73"/>
-      <c r="AE30" s="73"/>
+      <c r="Y30" s="74"/>
+      <c r="Z30" s="117" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA30" s="74"/>
+      <c r="AB30" s="74"/>
+      <c r="AC30" s="74"/>
+      <c r="AD30" s="74"/>
+      <c r="AE30" s="74"/>
     </row>
-    <row r="31" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A31" s="119" t="s">
-        <v>307</v>
-      </c>
-      <c r="B31" s="120"/>
-      <c r="C31" s="121"/>
-      <c r="D31" s="125">
+    <row r="31" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="120" t="s">
+        <v>312</v>
+      </c>
+      <c r="B31" s="121"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="126">
         <v>7493737</v>
       </c>
-      <c r="E31" s="73" t="str">
+      <c r="E31" s="74" t="str">
         <f t="shared" si="0"/>
         <v>1367493737</v>
       </c>
-      <c r="F31" s="73"/>
-      <c r="G31" s="103" t="s">
-        <v>308</v>
-      </c>
-      <c r="H31" s="116" t="s">
-        <v>309</v>
-      </c>
-      <c r="I31" s="103" t="s">
+      <c r="F31" s="74"/>
+      <c r="G31" s="104" t="s">
+        <v>313</v>
+      </c>
+      <c r="H31" s="117" t="s">
+        <v>314</v>
+      </c>
+      <c r="I31" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J31" s="103" t="s">
-        <v>310</v>
-      </c>
-      <c r="K31" s="116" t="s">
-        <v>311</v>
-      </c>
-      <c r="L31" s="73" t="s">
-        <v>312</v>
-      </c>
-      <c r="M31" s="122" t="s">
-        <v>313</v>
-      </c>
-      <c r="N31" s="126" t="s">
-        <v>314</v>
-      </c>
-      <c r="O31" s="106">
+      <c r="J31" s="104" t="s">
+        <v>315</v>
+      </c>
+      <c r="K31" s="117" t="s">
+        <v>316</v>
+      </c>
+      <c r="L31" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="M31" s="123" t="s">
+        <v>318</v>
+      </c>
+      <c r="N31" s="127" t="s">
+        <v>319</v>
+      </c>
+      <c r="O31" s="107">
         <v>45408</v>
       </c>
-      <c r="P31" s="123">
+      <c r="P31" s="124">
         <v>45474</v>
       </c>
-      <c r="Q31" s="123">
+      <c r="Q31" s="124">
         <v>45474</v>
       </c>
-      <c r="R31" s="113" t="s">
-        <v>315</v>
-      </c>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="104" t="s">
+      <c r="R31" s="114" t="s">
+        <v>320</v>
+      </c>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V31" s="103">
+      <c r="V31" s="104">
         <v>1</v>
       </c>
-      <c r="W31" s="103">
+      <c r="W31" s="104">
         <v>1</v>
       </c>
-      <c r="X31" s="73">
+      <c r="X31" s="74">
         <v>50607</v>
       </c>
-      <c r="Y31" s="73"/>
-      <c r="Z31" s="116"/>
-      <c r="AA31" s="73"/>
-      <c r="AB31" s="73"/>
-      <c r="AC31" s="73"/>
-      <c r="AD31" s="73"/>
-      <c r="AE31" s="73"/>
+      <c r="Y31" s="74"/>
+      <c r="Z31" s="117"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="74"/>
+      <c r="AD31" s="74"/>
+      <c r="AE31" s="74"/>
     </row>
-    <row r="32" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A32" s="119" t="s">
-        <v>316</v>
-      </c>
-      <c r="B32" s="117"/>
-      <c r="C32" s="121"/>
-      <c r="D32" s="125">
+    <row r="32" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="120" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="118"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="126">
         <v>7494263</v>
       </c>
-      <c r="E32" s="127" t="str">
+      <c r="E32" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367494263</v>
       </c>
-      <c r="F32" s="73"/>
-      <c r="G32" s="128" t="s">
-        <v>317</v>
-      </c>
-      <c r="H32" s="129" t="s">
-        <v>318</v>
-      </c>
-      <c r="I32" s="103" t="s">
+      <c r="F32" s="74"/>
+      <c r="G32" s="129" t="s">
+        <v>322</v>
+      </c>
+      <c r="H32" s="130" t="s">
+        <v>323</v>
+      </c>
+      <c r="I32" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J32" s="130" t="s">
-        <v>319</v>
-      </c>
-      <c r="K32" s="129" t="s">
-        <v>320</v>
-      </c>
-      <c r="L32" s="131" t="s">
-        <v>321</v>
-      </c>
-      <c r="M32" s="122" t="s">
-        <v>322</v>
-      </c>
-      <c r="N32" s="132" t="s">
-        <v>323</v>
-      </c>
-      <c r="O32" s="133">
+      <c r="J32" s="131" t="s">
+        <v>324</v>
+      </c>
+      <c r="K32" s="130" t="s">
+        <v>325</v>
+      </c>
+      <c r="L32" s="132" t="s">
+        <v>326</v>
+      </c>
+      <c r="M32" s="123" t="s">
+        <v>327</v>
+      </c>
+      <c r="N32" s="133" t="s">
+        <v>328</v>
+      </c>
+      <c r="O32" s="134">
         <v>45532</v>
       </c>
-      <c r="P32" s="106">
+      <c r="P32" s="107">
         <v>45658</v>
       </c>
-      <c r="Q32" s="106">
+      <c r="Q32" s="107">
         <v>45658</v>
       </c>
-      <c r="R32" s="113" t="s">
-        <v>324</v>
-      </c>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="U32" s="104" t="s">
+      <c r="R32" s="114" t="s">
+        <v>329</v>
+      </c>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
+      <c r="U32" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V32" s="103">
+      <c r="V32" s="104">
         <v>1</v>
       </c>
-      <c r="W32" s="103">
+      <c r="W32" s="104">
         <v>1</v>
       </c>
-      <c r="X32" s="73">
+      <c r="X32" s="74">
         <v>50701</v>
       </c>
-      <c r="Y32" s="73"/>
-      <c r="Z32" s="116"/>
-      <c r="AA32" s="73"/>
-      <c r="AB32" s="73"/>
-      <c r="AC32" s="73"/>
-      <c r="AD32" s="73"/>
-      <c r="AE32" s="73"/>
+      <c r="Y32" s="74"/>
+      <c r="Z32" s="117"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="74"/>
+      <c r="AD32" s="74"/>
+      <c r="AE32" s="74"/>
     </row>
-    <row r="33" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A33" s="119" t="s">
-        <v>325</v>
-      </c>
-      <c r="B33" s="117"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="125">
+    <row r="33" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="120" t="s">
+        <v>330</v>
+      </c>
+      <c r="B33" s="118"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="126">
         <v>7494677</v>
       </c>
-      <c r="E33" s="127" t="str">
+      <c r="E33" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367494677</v>
       </c>
-      <c r="F33" s="73"/>
-      <c r="G33" s="134" t="s">
-        <v>326</v>
-      </c>
-      <c r="H33" s="129" t="s">
-        <v>327</v>
-      </c>
-      <c r="I33" s="103" t="s">
+      <c r="F33" s="74"/>
+      <c r="G33" s="135" t="s">
+        <v>331</v>
+      </c>
+      <c r="H33" s="130" t="s">
+        <v>332</v>
+      </c>
+      <c r="I33" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J33" s="130" t="s">
-        <v>328</v>
-      </c>
-      <c r="K33" s="129" t="s">
+      <c r="J33" s="131" t="s">
+        <v>333</v>
+      </c>
+      <c r="K33" s="130" t="s">
+        <v>334</v>
+      </c>
+      <c r="L33" s="136" t="s">
+        <v>335</v>
+      </c>
+      <c r="M33" s="123" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33" s="137" t="s">
+        <v>336</v>
+      </c>
+      <c r="O33" s="134">
+        <v>45566</v>
+      </c>
+      <c r="P33" s="107">
+        <v>45658</v>
+      </c>
+      <c r="Q33" s="107">
+        <v>45658</v>
+      </c>
+      <c r="R33" s="114" t="s">
         <v>329</v>
       </c>
-      <c r="L33" s="135" t="s">
-        <v>330</v>
-      </c>
-      <c r="M33" s="122" t="s">
-        <v>40</v>
-      </c>
-      <c r="N33" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="O33" s="133">
-        <v>45566</v>
-      </c>
-      <c r="P33" s="106">
-        <v>45658</v>
-      </c>
-      <c r="Q33" s="106">
-        <v>45658</v>
-      </c>
-      <c r="R33" s="113" t="s">
-        <v>324</v>
-      </c>
-      <c r="S33" s="73"/>
-      <c r="T33" s="73"/>
-      <c r="U33" s="104" t="s">
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
+      <c r="U33" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V33" s="103">
+      <c r="V33" s="104">
         <v>1</v>
       </c>
-      <c r="W33" s="103">
+      <c r="W33" s="104">
         <v>1</v>
       </c>
-      <c r="X33" s="73">
+      <c r="X33" s="74">
         <v>50701</v>
       </c>
-      <c r="Y33" s="73"/>
-      <c r="Z33" s="116"/>
-      <c r="AA33" s="73"/>
-      <c r="AB33" s="73"/>
-      <c r="AC33" s="73"/>
-      <c r="AD33" s="73"/>
-      <c r="AE33" s="73"/>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="117"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="74"/>
+      <c r="AE33" s="74"/>
     </row>
-    <row r="34" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A34" s="119" t="s">
-        <v>332</v>
-      </c>
-      <c r="B34" s="117"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="125">
+    <row r="34" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="120" t="s">
+        <v>337</v>
+      </c>
+      <c r="B34" s="118"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="126">
         <v>7494388</v>
       </c>
-      <c r="E34" s="127" t="str">
+      <c r="E34" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367494388</v>
       </c>
-      <c r="F34" s="73"/>
-      <c r="G34" s="134" t="s">
-        <v>333</v>
-      </c>
-      <c r="H34" s="129" t="s">
-        <v>252</v>
-      </c>
-      <c r="I34" s="103" t="s">
+      <c r="F34" s="74"/>
+      <c r="G34" s="135" t="s">
+        <v>338</v>
+      </c>
+      <c r="H34" s="130" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J34" s="130" t="s">
-        <v>334</v>
-      </c>
-      <c r="K34" s="129" t="s">
-        <v>335</v>
-      </c>
-      <c r="L34" s="137" t="s">
-        <v>336</v>
-      </c>
-      <c r="M34" s="122" t="s">
-        <v>252</v>
-      </c>
-      <c r="N34" s="136" t="s">
-        <v>337</v>
-      </c>
-      <c r="O34" s="133">
+      <c r="J34" s="131" t="s">
+        <v>339</v>
+      </c>
+      <c r="K34" s="130" t="s">
+        <v>340</v>
+      </c>
+      <c r="L34" s="138" t="s">
+        <v>341</v>
+      </c>
+      <c r="M34" s="123" t="s">
+        <v>257</v>
+      </c>
+      <c r="N34" s="137" t="s">
+        <v>342</v>
+      </c>
+      <c r="O34" s="134">
         <v>45549</v>
       </c>
-      <c r="P34" s="106">
+      <c r="P34" s="107">
         <v>45658</v>
       </c>
-      <c r="Q34" s="106">
+      <c r="Q34" s="107">
         <v>45658</v>
       </c>
-      <c r="R34" s="113" t="s">
-        <v>324</v>
-      </c>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="104" t="s">
+      <c r="R34" s="114" t="s">
+        <v>329</v>
+      </c>
+      <c r="S34" s="74"/>
+      <c r="T34" s="74"/>
+      <c r="U34" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V34" s="103">
+      <c r="V34" s="104">
         <v>1</v>
       </c>
-      <c r="W34" s="103">
+      <c r="W34" s="104">
         <v>1</v>
       </c>
-      <c r="X34" s="73">
+      <c r="X34" s="74">
         <v>50701</v>
       </c>
-      <c r="Y34" s="73"/>
-      <c r="Z34" s="116"/>
-      <c r="AA34" s="73"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="73"/>
-      <c r="AD34" s="73"/>
-      <c r="AE34" s="73"/>
+      <c r="Y34" s="74"/>
+      <c r="Z34" s="117"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="74"/>
+      <c r="AC34" s="74"/>
+      <c r="AD34" s="74"/>
+      <c r="AE34" s="74"/>
     </row>
-    <row r="35" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A35" s="119" t="s">
-        <v>338</v>
-      </c>
-      <c r="B35" s="117"/>
-      <c r="C35" s="121" t="s">
-        <v>339</v>
-      </c>
-      <c r="D35" s="125">
+    <row r="35" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="120" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" s="118"/>
+      <c r="C35" s="122" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35" s="126">
         <v>7495146</v>
       </c>
-      <c r="E35" s="127" t="str">
+      <c r="E35" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367495146</v>
       </c>
-      <c r="F35" s="73"/>
-      <c r="G35" s="134" t="s">
-        <v>340</v>
-      </c>
-      <c r="H35" s="129" t="s">
-        <v>341</v>
-      </c>
-      <c r="I35" s="103" t="s">
+      <c r="F35" s="74"/>
+      <c r="G35" s="135" t="s">
+        <v>344</v>
+      </c>
+      <c r="H35" s="130" t="s">
+        <v>345</v>
+      </c>
+      <c r="I35" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J35" s="130" t="s">
-        <v>342</v>
-      </c>
-      <c r="K35" s="129" t="s">
-        <v>343</v>
-      </c>
-      <c r="L35" s="138" t="s">
-        <v>344</v>
-      </c>
-      <c r="M35" s="122" t="s">
-        <v>345</v>
-      </c>
-      <c r="N35" s="136" t="s">
-        <v>342</v>
-      </c>
-      <c r="O35" s="133">
+      <c r="J35" s="131" t="s">
+        <v>346</v>
+      </c>
+      <c r="K35" s="130" t="s">
+        <v>347</v>
+      </c>
+      <c r="L35" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="M35" s="123" t="s">
+        <v>349</v>
+      </c>
+      <c r="N35" s="137" t="s">
+        <v>346</v>
+      </c>
+      <c r="O35" s="134">
         <v>45652</v>
       </c>
-      <c r="P35" s="106">
+      <c r="P35" s="107">
         <v>45748</v>
       </c>
-      <c r="Q35" s="106">
+      <c r="Q35" s="107">
         <v>45748</v>
       </c>
-      <c r="R35" s="113" t="s">
-        <v>346</v>
-      </c>
-      <c r="S35" s="73"/>
-      <c r="T35" s="73"/>
-      <c r="U35" s="104" t="s">
+      <c r="R35" s="114" t="s">
+        <v>350</v>
+      </c>
+      <c r="S35" s="74"/>
+      <c r="T35" s="74"/>
+      <c r="U35" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V35" s="103">
+      <c r="V35" s="104">
         <v>1</v>
       </c>
-      <c r="W35" s="103">
+      <c r="W35" s="104">
         <v>1</v>
       </c>
-      <c r="X35" s="73">
+      <c r="X35" s="74">
         <v>50704</v>
       </c>
-      <c r="Y35" s="73">
+      <c r="Y35" s="74">
         <v>50803</v>
       </c>
-      <c r="Z35" s="116" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="73"/>
-      <c r="AC35" s="73"/>
-      <c r="AD35" s="73"/>
-      <c r="AE35" s="73"/>
+      <c r="Z35" s="117" t="s">
+        <v>351</v>
+      </c>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="74"/>
+      <c r="AD35" s="74"/>
+      <c r="AE35" s="74"/>
     </row>
-    <row r="36" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A36" s="119" t="s">
-        <v>348</v>
-      </c>
-      <c r="B36" s="117"/>
-      <c r="C36" s="121"/>
-      <c r="D36" s="125">
+    <row r="36" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="120" t="s">
+        <v>352</v>
+      </c>
+      <c r="B36" s="118"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="126">
         <v>7495989</v>
       </c>
-      <c r="E36" s="127" t="str">
+      <c r="E36" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367495989</v>
       </c>
-      <c r="F36" s="73"/>
-      <c r="G36" s="134" t="s">
-        <v>349</v>
-      </c>
-      <c r="H36" s="129" t="s">
-        <v>350</v>
-      </c>
-      <c r="I36" s="103" t="s">
+      <c r="F36" s="74"/>
+      <c r="G36" s="135" t="s">
+        <v>353</v>
+      </c>
+      <c r="H36" s="130" t="s">
+        <v>354</v>
+      </c>
+      <c r="I36" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="130" t="s">
-        <v>351</v>
-      </c>
-      <c r="K36" s="129" t="s">
-        <v>352</v>
-      </c>
-      <c r="L36" s="138" t="s">
-        <v>353</v>
-      </c>
-      <c r="M36" s="122" t="s">
-        <v>350</v>
-      </c>
-      <c r="N36" s="139" t="s">
-        <v>351</v>
-      </c>
-      <c r="O36" s="133">
+      <c r="J36" s="131" t="s">
+        <v>355</v>
+      </c>
+      <c r="K36" s="130" t="s">
+        <v>356</v>
+      </c>
+      <c r="L36" s="139" t="s">
+        <v>357</v>
+      </c>
+      <c r="M36" s="123" t="s">
+        <v>354</v>
+      </c>
+      <c r="N36" s="140" t="s">
+        <v>355</v>
+      </c>
+      <c r="O36" s="134">
         <v>45805</v>
       </c>
-      <c r="P36" s="106">
+      <c r="P36" s="107">
         <v>45931</v>
       </c>
-      <c r="Q36" s="106">
+      <c r="Q36" s="107">
         <v>45931</v>
       </c>
-      <c r="R36" s="102" t="s">
-        <v>354</v>
-      </c>
-      <c r="S36" s="73"/>
-      <c r="T36" s="73"/>
-      <c r="U36" s="104" t="s">
+      <c r="R36" s="103" t="s">
+        <v>358</v>
+      </c>
+      <c r="S36" s="74"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V36" s="103">
+      <c r="V36" s="104">
         <v>1</v>
       </c>
-      <c r="W36" s="103">
+      <c r="W36" s="104">
         <v>1</v>
       </c>
-      <c r="X36" s="73">
+      <c r="X36" s="74">
         <v>50710</v>
       </c>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="116"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="73"/>
-      <c r="AD36" s="73"/>
-      <c r="AE36" s="73"/>
+      <c r="Y36" s="74"/>
+      <c r="Z36" s="117"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="74"/>
+      <c r="AD36" s="74"/>
+      <c r="AE36" s="74"/>
     </row>
-    <row r="37" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A37" s="119" t="s">
-        <v>355</v>
-      </c>
-      <c r="B37" s="117"/>
-      <c r="C37" s="24" t="s">
+    <row r="37" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="120" t="s">
+        <v>359</v>
+      </c>
+      <c r="B37" s="118"/>
+      <c r="C37" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="125">
+      <c r="D37" s="126">
         <v>7496086</v>
       </c>
-      <c r="E37" s="127" t="str">
+      <c r="E37" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367496086</v>
       </c>
-      <c r="F37" s="73"/>
-      <c r="G37" s="134" t="s">
-        <v>356</v>
-      </c>
-      <c r="H37" s="129" t="s">
-        <v>357</v>
-      </c>
-      <c r="I37" s="103" t="s">
+      <c r="F37" s="74"/>
+      <c r="G37" s="135" t="s">
+        <v>360</v>
+      </c>
+      <c r="H37" s="130" t="s">
+        <v>361</v>
+      </c>
+      <c r="I37" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J37" s="130" t="s">
+      <c r="J37" s="131" t="s">
+        <v>362</v>
+      </c>
+      <c r="K37" s="130" t="s">
+        <v>363</v>
+      </c>
+      <c r="L37" s="139" t="s">
+        <v>364</v>
+      </c>
+      <c r="M37" s="123" t="s">
+        <v>361</v>
+      </c>
+      <c r="N37" s="141" t="s">
+        <v>362</v>
+      </c>
+      <c r="O37" s="134">
+        <v>45834</v>
+      </c>
+      <c r="P37" s="107">
+        <v>45931</v>
+      </c>
+      <c r="Q37" s="107">
+        <v>45931</v>
+      </c>
+      <c r="R37" s="103" t="s">
         <v>358</v>
       </c>
-      <c r="K37" s="129" t="s">
-        <v>359</v>
-      </c>
-      <c r="L37" s="138" t="s">
-        <v>360</v>
-      </c>
-      <c r="M37" s="122" t="s">
-        <v>357</v>
-      </c>
-      <c r="N37" s="140" t="s">
-        <v>358</v>
-      </c>
-      <c r="O37" s="133">
-        <v>45834</v>
-      </c>
-      <c r="P37" s="106">
-        <v>45931</v>
-      </c>
-      <c r="Q37" s="106">
-        <v>45931</v>
-      </c>
-      <c r="R37" s="102" t="s">
-        <v>354</v>
-      </c>
-      <c r="S37" s="73"/>
-      <c r="T37" s="73"/>
-      <c r="U37" s="104" t="s">
+      <c r="S37" s="74"/>
+      <c r="T37" s="74"/>
+      <c r="U37" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="V37" s="103">
+      <c r="V37" s="104">
         <v>0</v>
       </c>
-      <c r="W37" s="103">
+      <c r="W37" s="104">
         <v>1</v>
       </c>
-      <c r="X37" s="73">
+      <c r="X37" s="74">
         <v>50710</v>
       </c>
-      <c r="Y37" s="103">
+      <c r="Y37" s="104">
         <v>50712</v>
       </c>
-      <c r="Z37" s="116" t="s">
-        <v>361</v>
-      </c>
-      <c r="AA37" s="73"/>
-      <c r="AB37" s="73"/>
-      <c r="AC37" s="73"/>
-      <c r="AD37" s="73"/>
-      <c r="AE37" s="73"/>
+      <c r="Z37" s="117" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA37" s="74"/>
+      <c r="AB37" s="74"/>
+      <c r="AC37" s="74"/>
+      <c r="AD37" s="74"/>
+      <c r="AE37" s="74"/>
     </row>
-    <row r="38" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A38" s="119" t="s">
-        <v>362</v>
-      </c>
-      <c r="B38" s="117"/>
-      <c r="C38" s="121"/>
-      <c r="D38" s="125">
+    <row r="38" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="120" t="s">
+        <v>366</v>
+      </c>
+      <c r="B38" s="118"/>
+      <c r="C38" s="122"/>
+      <c r="D38" s="126">
         <v>7496086</v>
       </c>
-      <c r="E38" s="127" t="str">
+      <c r="E38" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367496086</v>
       </c>
-      <c r="F38" s="73"/>
-      <c r="G38" s="134" t="s">
-        <v>356</v>
-      </c>
-      <c r="H38" s="129" t="s">
-        <v>357</v>
-      </c>
-      <c r="I38" s="103" t="s">
+      <c r="F38" s="74"/>
+      <c r="G38" s="135" t="s">
+        <v>360</v>
+      </c>
+      <c r="H38" s="130" t="s">
+        <v>361</v>
+      </c>
+      <c r="I38" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J38" s="130" t="s">
-        <v>358</v>
-      </c>
-      <c r="K38" s="129" t="s">
-        <v>359</v>
-      </c>
-      <c r="L38" s="138" t="s">
-        <v>360</v>
-      </c>
-      <c r="M38" s="122" t="s">
-        <v>357</v>
-      </c>
-      <c r="N38" s="140" t="s">
-        <v>358</v>
-      </c>
-      <c r="O38" s="133">
+      <c r="J38" s="131" t="s">
+        <v>362</v>
+      </c>
+      <c r="K38" s="130" t="s">
+        <v>363</v>
+      </c>
+      <c r="L38" s="139" t="s">
+        <v>364</v>
+      </c>
+      <c r="M38" s="123" t="s">
+        <v>361</v>
+      </c>
+      <c r="N38" s="141" t="s">
+        <v>362</v>
+      </c>
+      <c r="O38" s="134">
         <v>45932</v>
       </c>
-      <c r="P38" s="106">
+      <c r="P38" s="107">
         <v>46023</v>
       </c>
-      <c r="Q38" s="106">
+      <c r="Q38" s="107">
         <v>46023</v>
       </c>
-      <c r="R38" s="102" t="s">
-        <v>363</v>
-      </c>
-      <c r="S38" s="73"/>
-      <c r="T38" s="73"/>
-      <c r="U38" s="104" t="s">
+      <c r="R38" s="103" t="s">
+        <v>367</v>
+      </c>
+      <c r="S38" s="74"/>
+      <c r="T38" s="74"/>
+      <c r="U38" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V38" s="103">
+      <c r="V38" s="104">
         <v>1</v>
       </c>
-      <c r="W38" s="103">
+      <c r="W38" s="104">
         <v>1</v>
       </c>
-      <c r="X38" s="73">
+      <c r="X38" s="74">
         <v>50801</v>
       </c>
-      <c r="Y38" s="103"/>
-      <c r="Z38" s="116"/>
-      <c r="AA38" s="73"/>
-      <c r="AB38" s="73"/>
-      <c r="AC38" s="73"/>
-      <c r="AD38" s="73"/>
-      <c r="AE38" s="73"/>
+      <c r="Y38" s="104"/>
+      <c r="Z38" s="117"/>
+      <c r="AA38" s="74"/>
+      <c r="AB38" s="74"/>
+      <c r="AC38" s="74"/>
+      <c r="AD38" s="74"/>
+      <c r="AE38" s="74"/>
     </row>
-    <row r="39" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A39" s="119" t="s">
-        <v>364</v>
-      </c>
-      <c r="B39" s="117"/>
-      <c r="C39" s="121"/>
-      <c r="D39" s="141">
+    <row r="39" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="120" t="s">
+        <v>368</v>
+      </c>
+      <c r="B39" s="118"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="142">
         <v>7496698</v>
       </c>
-      <c r="E39" s="127" t="str">
+      <c r="E39" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367496698</v>
       </c>
-      <c r="F39" s="73"/>
-      <c r="G39" s="134" t="s">
-        <v>365</v>
-      </c>
-      <c r="H39" s="129" t="s">
-        <v>366</v>
-      </c>
-      <c r="I39" s="103" t="s">
+      <c r="F39" s="74"/>
+      <c r="G39" s="135" t="s">
+        <v>369</v>
+      </c>
+      <c r="H39" s="130" t="s">
+        <v>370</v>
+      </c>
+      <c r="I39" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J39" s="130" t="s">
+      <c r="J39" s="131" t="s">
+        <v>371</v>
+      </c>
+      <c r="K39" s="130" t="s">
+        <v>372</v>
+      </c>
+      <c r="L39" s="139" t="s">
+        <v>373</v>
+      </c>
+      <c r="M39" s="123" t="s">
+        <v>374</v>
+      </c>
+      <c r="N39" s="141" t="s">
+        <v>375</v>
+      </c>
+      <c r="O39" s="134">
+        <v>45931</v>
+      </c>
+      <c r="P39" s="107">
+        <v>46023</v>
+      </c>
+      <c r="Q39" s="107">
+        <v>46023</v>
+      </c>
+      <c r="R39" s="103" t="s">
         <v>367</v>
       </c>
-      <c r="K39" s="129" t="s">
-        <v>368</v>
-      </c>
-      <c r="L39" s="138" t="s">
-        <v>369</v>
-      </c>
-      <c r="M39" s="122" t="s">
-        <v>370</v>
-      </c>
-      <c r="N39" s="140" t="s">
-        <v>371</v>
-      </c>
-      <c r="O39" s="133">
-        <v>45931</v>
-      </c>
-      <c r="P39" s="106">
-        <v>46023</v>
-      </c>
-      <c r="Q39" s="106">
-        <v>46023</v>
-      </c>
-      <c r="R39" s="102" t="s">
-        <v>363</v>
-      </c>
-      <c r="S39" s="73"/>
-      <c r="T39" s="73"/>
-      <c r="U39" s="104" t="s">
+      <c r="S39" s="74"/>
+      <c r="T39" s="74"/>
+      <c r="U39" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V39" s="103">
+      <c r="V39" s="104">
         <v>1</v>
       </c>
-      <c r="W39" s="103">
+      <c r="W39" s="104">
         <v>1</v>
       </c>
-      <c r="X39" s="73">
+      <c r="X39" s="74">
         <v>50801</v>
       </c>
-      <c r="Y39" s="103"/>
-      <c r="Z39" s="116"/>
-      <c r="AA39" s="73"/>
-      <c r="AB39" s="73"/>
-      <c r="AC39" s="73"/>
-      <c r="AD39" s="73"/>
-      <c r="AE39" s="73"/>
+      <c r="Y39" s="104"/>
+      <c r="Z39" s="117"/>
+      <c r="AA39" s="74"/>
+      <c r="AB39" s="74"/>
+      <c r="AC39" s="74"/>
+      <c r="AD39" s="74"/>
+      <c r="AE39" s="74"/>
     </row>
-    <row r="40" spans="1:31" ht="72">
-      <c r="A40" s="119" t="s">
-        <v>372</v>
-      </c>
-      <c r="B40" s="112"/>
-      <c r="C40" s="121"/>
-      <c r="D40" s="141">
+    <row r="40" spans="1:31" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A40" s="120" t="s">
+        <v>376</v>
+      </c>
+      <c r="B40" s="113"/>
+      <c r="C40" s="122"/>
+      <c r="D40" s="142">
         <v>7496276</v>
       </c>
-      <c r="E40" s="127" t="str">
+      <c r="E40" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367496276</v>
       </c>
-      <c r="F40" s="73"/>
-      <c r="G40" s="134" t="s">
-        <v>373</v>
-      </c>
-      <c r="H40" s="129" t="s">
-        <v>341</v>
-      </c>
-      <c r="I40" s="103" t="s">
+      <c r="F40" s="74"/>
+      <c r="G40" s="135" t="s">
+        <v>377</v>
+      </c>
+      <c r="H40" s="130" t="s">
+        <v>345</v>
+      </c>
+      <c r="I40" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="130" t="s">
-        <v>374</v>
-      </c>
-      <c r="K40" s="129" t="s">
-        <v>375</v>
-      </c>
-      <c r="L40" s="138" t="s">
-        <v>376</v>
-      </c>
-      <c r="M40" s="122" t="s">
-        <v>377</v>
-      </c>
-      <c r="N40" s="140" t="s">
+      <c r="J40" s="131" t="s">
         <v>378</v>
       </c>
-      <c r="O40" s="133">
+      <c r="K40" s="130" t="s">
+        <v>379</v>
+      </c>
+      <c r="L40" s="139" t="s">
+        <v>380</v>
+      </c>
+      <c r="M40" s="123" t="s">
+        <v>381</v>
+      </c>
+      <c r="N40" s="141" t="s">
+        <v>382</v>
+      </c>
+      <c r="O40" s="134">
         <v>45936</v>
       </c>
-      <c r="P40" s="106">
+      <c r="P40" s="107">
         <v>46023</v>
       </c>
-      <c r="Q40" s="106">
+      <c r="Q40" s="107">
         <v>46023</v>
       </c>
-      <c r="R40" s="102" t="s">
-        <v>363</v>
-      </c>
-      <c r="S40" s="73"/>
-      <c r="T40" s="73"/>
-      <c r="U40" s="104" t="s">
+      <c r="R40" s="103" t="s">
+        <v>367</v>
+      </c>
+      <c r="S40" s="74"/>
+      <c r="T40" s="74"/>
+      <c r="U40" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V40" s="103">
+      <c r="V40" s="104">
         <v>1</v>
       </c>
-      <c r="W40" s="103">
+      <c r="W40" s="104">
         <v>1</v>
       </c>
-      <c r="X40" s="73">
+      <c r="X40" s="74">
         <v>50801</v>
       </c>
-      <c r="Y40" s="103"/>
-      <c r="Z40" s="116" t="s">
-        <v>379</v>
-      </c>
-      <c r="AA40" s="73"/>
-      <c r="AB40" s="73"/>
-      <c r="AC40" s="73"/>
-      <c r="AD40" s="73"/>
-      <c r="AE40" s="73"/>
+      <c r="Y40" s="104"/>
+      <c r="Z40" s="117" t="s">
+        <v>383</v>
+      </c>
+      <c r="AA40" s="74"/>
+      <c r="AB40" s="74"/>
+      <c r="AC40" s="74"/>
+      <c r="AD40" s="74"/>
+      <c r="AE40" s="74"/>
     </row>
-    <row r="41" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A41" s="119" t="s">
-        <v>380</v>
-      </c>
-      <c r="B41" s="117"/>
-      <c r="C41" s="121"/>
-      <c r="D41" s="141">
+    <row r="41" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="120" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41" s="118"/>
+      <c r="C41" s="122"/>
+      <c r="D41" s="142">
         <v>7496680</v>
       </c>
-      <c r="E41" s="127" t="str">
+      <c r="E41" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367496680</v>
       </c>
-      <c r="F41" s="73"/>
-      <c r="G41" s="134" t="s">
-        <v>381</v>
-      </c>
-      <c r="H41" s="129" t="s">
-        <v>382</v>
-      </c>
-      <c r="I41" s="103" t="s">
+      <c r="F41" s="74"/>
+      <c r="G41" s="135" t="s">
+        <v>385</v>
+      </c>
+      <c r="H41" s="130" t="s">
+        <v>386</v>
+      </c>
+      <c r="I41" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="130" t="s">
-        <v>383</v>
-      </c>
-      <c r="K41" s="129" t="s">
-        <v>384</v>
-      </c>
-      <c r="L41" s="138" t="s">
-        <v>385</v>
-      </c>
-      <c r="M41" s="122" t="s">
-        <v>386</v>
-      </c>
-      <c r="N41" s="140" t="s">
+      <c r="J41" s="131" t="s">
         <v>387</v>
       </c>
-      <c r="O41" s="133">
+      <c r="K41" s="130" t="s">
+        <v>388</v>
+      </c>
+      <c r="L41" s="139" t="s">
+        <v>389</v>
+      </c>
+      <c r="M41" s="123" t="s">
+        <v>390</v>
+      </c>
+      <c r="N41" s="141" t="s">
+        <v>391</v>
+      </c>
+      <c r="O41" s="134">
         <v>46065</v>
       </c>
-      <c r="P41" s="106">
+      <c r="P41" s="107">
         <v>46113</v>
       </c>
-      <c r="Q41" s="106">
+      <c r="Q41" s="107">
         <v>46113</v>
       </c>
-      <c r="R41" s="102" t="s">
-        <v>388</v>
-      </c>
-      <c r="S41" s="73"/>
-      <c r="T41" s="73"/>
-      <c r="U41" s="104" t="s">
+      <c r="R41" s="103" t="s">
+        <v>392</v>
+      </c>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V41" s="103">
+      <c r="V41" s="104">
         <v>1</v>
       </c>
-      <c r="W41" s="103">
+      <c r="W41" s="104">
         <v>1</v>
       </c>
-      <c r="X41" s="73">
+      <c r="X41" s="74">
         <v>50804</v>
       </c>
-      <c r="Y41" s="103"/>
-      <c r="Z41" s="116"/>
-      <c r="AA41" s="73"/>
-      <c r="AB41" s="73"/>
-      <c r="AC41" s="73"/>
-      <c r="AD41" s="73"/>
-      <c r="AE41" s="73"/>
+      <c r="Y41" s="104"/>
+      <c r="Z41" s="117"/>
+      <c r="AA41" s="74"/>
+      <c r="AB41" s="74"/>
+      <c r="AC41" s="74"/>
+      <c r="AD41" s="74"/>
+      <c r="AE41" s="74"/>
     </row>
-    <row r="42" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A42" s="119" t="s">
-        <v>389</v>
-      </c>
-      <c r="B42" s="117"/>
-      <c r="C42" s="121"/>
-      <c r="D42" s="141">
+    <row r="42" spans="1:31" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="120" t="s">
+        <v>393</v>
+      </c>
+      <c r="B42" s="118"/>
+      <c r="C42" s="122"/>
+      <c r="D42" s="142">
         <v>7497332</v>
       </c>
-      <c r="E42" s="127" t="str">
+      <c r="E42" s="128" t="str">
         <f t="shared" si="0"/>
         <v>1367497332</v>
       </c>
-      <c r="F42" s="73"/>
-      <c r="G42" s="134" t="s">
-        <v>390</v>
-      </c>
-      <c r="H42" s="129" t="s">
-        <v>391</v>
-      </c>
-      <c r="I42" s="103" t="s">
+      <c r="F42" s="74"/>
+      <c r="G42" s="135" t="s">
+        <v>394</v>
+      </c>
+      <c r="H42" s="130" t="s">
+        <v>395</v>
+      </c>
+      <c r="I42" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="J42" s="130" t="s">
+      <c r="J42" s="131" t="s">
+        <v>396</v>
+      </c>
+      <c r="K42" s="130" t="s">
+        <v>397</v>
+      </c>
+      <c r="L42" s="139" t="s">
+        <v>335</v>
+      </c>
+      <c r="M42" s="123" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="137" t="s">
+        <v>336</v>
+      </c>
+      <c r="O42" s="134">
+        <v>46065</v>
+      </c>
+      <c r="P42" s="107">
+        <v>46113</v>
+      </c>
+      <c r="Q42" s="107">
+        <v>46113</v>
+      </c>
+      <c r="R42" s="103" t="s">
         <v>392</v>
       </c>
-      <c r="K42" s="129" t="s">
-        <v>393</v>
-      </c>
-      <c r="L42" s="138" t="s">
-        <v>330</v>
-      </c>
-      <c r="M42" s="122" t="s">
-        <v>40</v>
-      </c>
-      <c r="N42" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="O42" s="133">
-        <v>46065</v>
-      </c>
-      <c r="P42" s="106">
-        <v>46113</v>
-      </c>
-      <c r="Q42" s="106">
-        <v>46113</v>
-      </c>
-      <c r="R42" s="102" t="s">
-        <v>388</v>
-      </c>
-      <c r="S42" s="73"/>
-      <c r="T42" s="73"/>
-      <c r="U42" s="104" t="s">
+      <c r="S42" s="74"/>
+      <c r="T42" s="74"/>
+      <c r="U42" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="V42" s="103">
+      <c r="V42" s="104">
         <v>1</v>
       </c>
-      <c r="W42" s="103">
+      <c r="W42" s="104">
         <v>1</v>
       </c>
-      <c r="X42" s="73">
+      <c r="X42" s="74">
         <v>50804</v>
       </c>
-      <c r="Y42" s="103"/>
-      <c r="Z42" s="116"/>
-      <c r="AA42" s="73"/>
-      <c r="AB42" s="73"/>
-      <c r="AC42" s="73"/>
-      <c r="AD42" s="73"/>
-      <c r="AE42" s="73"/>
+      <c r="Y42" s="104"/>
+      <c r="Z42" s="117"/>
+      <c r="AA42" s="74"/>
+      <c r="AB42" s="74"/>
+      <c r="AC42" s="74"/>
+      <c r="AD42" s="74"/>
+      <c r="AE42" s="74"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD42" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:AF47" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="21">
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="AD2:AD3"/>
@@ -8685,14 +8653,13 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <dataValidations count="1">
-    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F28" xr:uid="{54BA6A40-4501-4932-A17A-A74DEEE9675E}"/>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F28" xr:uid="{5A2514AA-93B1-489D-876A-731EF01475D4}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="37" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="18" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>